--- a/inasistencias-6A-Tc/Alumnos-6A-Tc.xlsx
+++ b/inasistencias-6A-Tc/Alumnos-6A-Tc.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="350">
   <si>
     <t xml:space="preserve">Teocra de circuitos</t>
   </si>
@@ -352,6 +352,18 @@
   </si>
   <si>
     <t xml:space="preserve">Asistencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carpeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-calculo l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- cto C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- Cto D</t>
   </si>
   <si>
     <t xml:space="preserve">Recuperacion agosto</t>
@@ -1443,18 +1455,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM30"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AP30"/>
+  <sheetFormatPr defaultColWidth="8.91796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="3" style="1" width="33.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="3" style="1" width="33.13"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="5" style="1" width="8.62"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="11" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="18" style="1" width="8.69"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="25" style="1" width="8.84"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="29" style="1" width="8.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="13.76"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="29" style="1" width="8.87"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="35" style="1" width="8.92"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="36" min="36" style="1" width="13.76"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="38" min="37" style="1" width="8.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1590,11 +1604,20 @@
       <c r="AL3" s="3" t="n">
         <v>45936</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AM3" s="3" t="n">
         <v>45943</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN3" s="3" t="n">
+        <v>45947</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>45950</v>
+      </c>
+      <c r="AP3" s="4" t="n">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -1696,11 +1719,20 @@
       <c r="AL4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM4" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
@@ -1799,11 +1831,20 @@
       <c r="AL5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM5" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
@@ -1905,11 +1946,20 @@
       <c r="AL6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM6" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
@@ -2008,11 +2058,20 @@
       <c r="AL7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
@@ -2111,11 +2170,20 @@
       <c r="AL8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP8" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
@@ -2214,11 +2282,20 @@
       <c r="AL9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AM9" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
@@ -2320,11 +2397,20 @@
       <c r="AL10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM10" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
@@ -2423,11 +2509,20 @@
       <c r="AL11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM11" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP11" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
@@ -2526,11 +2621,20 @@
       <c r="AL12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM12" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
@@ -2629,11 +2733,20 @@
       <c r="AL13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM13" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
@@ -2735,11 +2848,20 @@
       <c r="AL14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM14" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
@@ -2838,11 +2960,20 @@
       <c r="AL15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM15" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
@@ -2947,11 +3078,20 @@
       <c r="AL16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
@@ -3050,11 +3190,20 @@
       <c r="AL17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM17" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP17" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
@@ -3153,11 +3302,20 @@
       <c r="AL18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM18" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP18" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
@@ -3256,11 +3414,20 @@
       <c r="AL19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AM19" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP19" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
@@ -3359,11 +3526,20 @@
       <c r="AL20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM20" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP20" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
@@ -3462,11 +3638,20 @@
       <c r="AL21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM21" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
@@ -3565,11 +3750,20 @@
       <c r="AL22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM22" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP22" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
@@ -3671,11 +3865,20 @@
       <c r="AL23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM23" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP23" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
@@ -3774,11 +3977,20 @@
       <c r="AL24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM24" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP24" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
@@ -3880,11 +4092,20 @@
       <c r="AL25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM25" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
@@ -3983,11 +4204,20 @@
       <c r="AL26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM26" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP26" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
@@ -4089,11 +4319,20 @@
       <c r="AL27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM27" s="6" t="s">
+      <c r="AM27" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
@@ -4192,11 +4431,20 @@
       <c r="AL28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM28" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP28" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>26</v>
       </c>
@@ -4298,8 +4546,17 @@
       <c r="AL29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM29" s="6" t="s">
-        <v>13</v>
+      <c r="AM29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP29" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4410,6 +4667,18 @@
       <c r="AM30" s="1" t="n">
         <f aca="false">COUNTIF(AM4:AM29,"P")</f>
         <v>20</v>
+      </c>
+      <c r="AN30" s="1" t="n">
+        <f aca="false">COUNTIF(AN4:AN29,"P")</f>
+        <v>24</v>
+      </c>
+      <c r="AO30" s="1" t="n">
+        <f aca="false">COUNTIF(AO4:AO29,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AP30" s="1" t="n">
+        <f aca="false">COUNTIF(AP4:AP29,"P")</f>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4433,12 +4702,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="17" min="3" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="1" width="18.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="19" style="1" width="9.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4502,8 +4773,20 @@
       <c r="T1" s="3" t="n">
         <v>45877</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U1" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -4548,7 +4831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -4598,8 +4881,9 @@
       <c r="T3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -4650,13 +4934,13 @@
         <v>7</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
@@ -4701,7 +4985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -4751,8 +5035,9 @@
       <c r="T6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -4802,8 +5087,9 @@
       <c r="T7" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
@@ -4848,7 +5134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
@@ -4893,7 +5179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
@@ -4938,7 +5224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
@@ -4995,7 +5281,7 @@
         <v>7</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>13</v>
@@ -5003,8 +5289,9 @@
       <c r="T11" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>26</v>
       </c>
@@ -5049,7 +5336,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -5094,7 +5381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
@@ -5139,7 +5426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -5184,7 +5471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
@@ -5235,7 +5522,7 @@
         <v>7</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>13</v>
@@ -5243,8 +5530,9 @@
       <c r="T16" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
@@ -5289,7 +5577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
@@ -5334,7 +5622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -5379,7 +5667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -5424,7 +5712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -5474,8 +5762,9 @@
       <c r="T21" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
@@ -5520,7 +5809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
@@ -5565,7 +5854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
@@ -5610,7 +5899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
@@ -5655,7 +5944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
@@ -5700,7 +5989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
@@ -5782,7 +6071,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="19.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.47"/>
   </cols>
   <sheetData>
@@ -5791,22 +6080,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5820,10 +6109,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -5857,10 +6146,10 @@
         <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -5882,10 +6171,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -5902,10 +6191,10 @@
         <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -5927,10 +6216,10 @@
         <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -5975,10 +6264,10 @@
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -6000,10 +6289,10 @@
         <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -6014,10 +6303,10 @@
         <v>31</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -6028,10 +6317,10 @@
         <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>4</v>
@@ -6042,10 +6331,10 @@
         <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>4</v>
@@ -6062,10 +6351,10 @@
         <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -6085,10 +6374,10 @@
         <v>38</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -6122,10 +6411,10 @@
         <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -6145,10 +6434,10 @@
         <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -6168,10 +6457,10 @@
         <v>50</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -6193,10 +6482,10 @@
         <v>50</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -6213,10 +6502,10 @@
         <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -6238,10 +6527,10 @@
         <v>54</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -6252,10 +6541,10 @@
         <v>54</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -6266,10 +6555,10 @@
         <v>54</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -6280,10 +6569,10 @@
         <v>54</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -6294,10 +6583,10 @@
         <v>54</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>5</v>
@@ -6308,10 +6597,10 @@
         <v>54</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>3</v>
@@ -6328,10 +6617,10 @@
         <v>57</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -6353,10 +6642,10 @@
         <v>57</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>6</v>
@@ -6373,10 +6662,10 @@
         <v>60</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -6398,10 +6687,10 @@
         <v>60</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>8</v>
@@ -6412,10 +6701,10 @@
         <v>60</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>6</v>
@@ -6426,10 +6715,10 @@
         <v>60</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4</v>
@@ -6440,10 +6729,10 @@
         <v>60</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>2</v>
@@ -6454,10 +6743,10 @@
         <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>2</v>
@@ -6474,10 +6763,10 @@
         <v>64</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -6497,10 +6786,10 @@
         <v>67</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -6522,10 +6811,10 @@
         <v>67</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>5</v>
@@ -6542,10 +6831,10 @@
         <v>70</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -6567,10 +6856,10 @@
         <v>70</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>5</v>
@@ -6587,10 +6876,10 @@
         <v>73</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -6612,10 +6901,10 @@
         <v>73</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>8</v>
@@ -6626,10 +6915,10 @@
         <v>73</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>8</v>
@@ -6640,10 +6929,10 @@
         <v>73</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>4</v>
@@ -6660,10 +6949,10 @@
         <v>77</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>10</v>
@@ -6683,10 +6972,10 @@
         <v>80</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>10</v>
@@ -6708,10 +6997,10 @@
         <v>80</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>9</v>
@@ -6722,10 +7011,10 @@
         <v>80</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>9</v>
@@ -6736,10 +7025,10 @@
         <v>80</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>5</v>
@@ -6750,10 +7039,10 @@
         <v>80</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>4</v>
@@ -6770,10 +7059,10 @@
         <v>83</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>10</v>
@@ -6795,10 +7084,10 @@
         <v>83</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>7</v>
@@ -6815,10 +7104,10 @@
         <v>86</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>10</v>
@@ -6838,10 +7127,10 @@
         <v>91</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>8</v>
@@ -6861,10 +7150,10 @@
         <v>94</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>7</v>
@@ -6893,7 +7182,7 @@
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
@@ -6903,22 +7192,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6932,10 +7221,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -6957,10 +7246,10 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -6991,10 +7280,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -7014,10 +7303,10 @@
         <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -7065,10 +7354,10 @@
         <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -7088,10 +7377,10 @@
         <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -7111,10 +7400,10 @@
         <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>9</v>
@@ -7136,10 +7425,10 @@
         <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>9</v>
@@ -7150,10 +7439,10 @@
         <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -7164,10 +7453,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>2</v>
@@ -7184,10 +7473,10 @@
         <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>1</v>
@@ -7207,10 +7496,10 @@
         <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -7230,10 +7519,10 @@
         <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -7253,10 +7542,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -7278,10 +7567,10 @@
         <v>50</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -7292,10 +7581,10 @@
         <v>50</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -7306,10 +7595,10 @@
         <v>50</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -7320,10 +7609,10 @@
         <v>50</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>3</v>
@@ -7334,10 +7623,10 @@
         <v>50</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>0</v>
@@ -7354,10 +7643,10 @@
         <v>54</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>5</v>
@@ -7377,10 +7666,10 @@
         <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -7400,10 +7689,10 @@
         <v>60</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>8</v>
@@ -7423,10 +7712,10 @@
         <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -7446,10 +7735,10 @@
         <v>67</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -7471,10 +7760,10 @@
         <v>67</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -7485,10 +7774,10 @@
         <v>67</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0</v>
@@ -7505,10 +7794,10 @@
         <v>70</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>8</v>
@@ -7528,10 +7817,10 @@
         <v>73</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>1</v>
@@ -7551,10 +7840,10 @@
         <v>77</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -7576,10 +7865,10 @@
         <v>77</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -7590,10 +7879,10 @@
         <v>77</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -7604,10 +7893,10 @@
         <v>77</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>6</v>
@@ -7618,10 +7907,10 @@
         <v>77</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>1</v>
@@ -7638,10 +7927,10 @@
         <v>80</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>10</v>
@@ -7663,10 +7952,10 @@
         <v>80</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>9</v>
@@ -7677,10 +7966,10 @@
         <v>80</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>8</v>
@@ -7691,10 +7980,10 @@
         <v>80</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>2</v>
@@ -7711,10 +8000,10 @@
         <v>83</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>9</v>
@@ -7734,10 +8023,10 @@
         <v>86</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -7759,10 +8048,10 @@
         <v>86</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -7773,10 +8062,10 @@
         <v>86</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7</v>
@@ -7793,10 +8082,10 @@
         <v>91</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>9</v>
@@ -7818,10 +8107,10 @@
         <v>91</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>6</v>
@@ -7838,10 +8127,10 @@
         <v>94</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>7</v>
@@ -7870,7 +8159,7 @@
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7878,22 +8167,22 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7901,10 +8190,10 @@
         <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -7926,10 +8215,10 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>8</v>
@@ -7940,10 +8229,10 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>8</v>
@@ -7954,10 +8243,10 @@
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -7979,11 +8268,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="3" style="1" width="9.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1005" style="1" width="9.33"/>
   </cols>
@@ -8227,6 +8516,9 @@
       <c r="J11" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="L11" s="0" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -8274,6 +8566,9 @@
         <f aca="false">SUM(E13:H13)</f>
         <v>8</v>
       </c>
+      <c r="L13" s="0" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -8296,6 +8591,9 @@
         <f aca="false">SUM(E14:H14)</f>
         <v>5</v>
       </c>
+      <c r="L14" s="0" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -8324,6 +8622,9 @@
       <c r="K15" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="L15" s="0" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -8518,6 +8819,9 @@
       <c r="K24" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="L24" s="0" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -8547,6 +8851,9 @@
       </c>
       <c r="J25" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8613,10 +8920,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="9.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5546875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.87"/>
@@ -8630,19 +8937,19 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8659,7 +8966,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -8710,7 +9017,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -8733,7 +9040,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -8756,7 +9063,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -8779,7 +9086,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -8802,7 +9109,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -8825,7 +9132,7 @@
         <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -8862,7 +9169,7 @@
         <v>45</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -8885,7 +9192,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -8908,7 +9215,7 @@
         <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8</v>
@@ -8931,7 +9238,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -8968,7 +9275,7 @@
         <v>61</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -8991,7 +9298,7 @@
         <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -9016,7 +9323,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -9036,7 +9343,7 @@
         <v>68</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -9061,7 +9368,7 @@
         <v>68</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -9075,7 +9382,7 @@
         <v>68</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>5</v>
@@ -9089,7 +9396,7 @@
         <v>68</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4</v>
@@ -9109,7 +9416,7 @@
         <v>71</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -9132,7 +9439,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -9155,7 +9462,7 @@
         <v>78</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -9178,7 +9485,7 @@
         <v>81</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -9201,7 +9508,7 @@
         <v>84</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -9224,7 +9531,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -9287,7 +9594,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="9.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5546875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.83"/>
@@ -9303,10 +9610,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9356,7 +9663,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -9387,7 +9694,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -9407,7 +9714,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -9427,7 +9734,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9447,7 +9754,7 @@
         <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -9489,7 +9796,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -9509,7 +9816,7 @@
         <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -9529,7 +9836,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -9560,7 +9867,7 @@
         <v>61</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -9580,7 +9887,7 @@
         <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -9600,7 +9907,7 @@
         <v>68</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -9620,7 +9927,7 @@
         <v>71</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -9673,7 +9980,7 @@
         <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -9693,7 +10000,7 @@
         <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -9713,7 +10020,7 @@
         <v>92</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -9730,10 +10037,10 @@
         <v>94</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -9765,7 +10072,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5546875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.83"/>
@@ -9780,10 +10087,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9800,7 +10107,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -9820,7 +10127,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>5.29</v>
@@ -9840,7 +10147,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8.04</v>
@@ -9860,7 +10167,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>5.49</v>
@@ -9891,7 +10198,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3.53</v>
@@ -9911,7 +10218,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7.84</v>
@@ -9931,7 +10238,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7.45</v>
@@ -9951,7 +10258,7 @@
         <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -9971,7 +10278,7 @@
         <v>42</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>5.69</v>
@@ -9991,7 +10298,7 @@
         <v>45</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7.84</v>
@@ -10011,7 +10318,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -10031,7 +10338,7 @@
         <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8.43</v>
@@ -10051,7 +10358,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6.86</v>
@@ -10071,7 +10378,7 @@
         <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9.61</v>
@@ -10091,7 +10398,7 @@
         <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>7.45</v>
@@ -10122,7 +10429,7 @@
         <v>68</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7.84</v>
@@ -10142,7 +10449,7 @@
         <v>71</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.24</v>
@@ -10162,7 +10469,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>5.1</v>
@@ -10182,7 +10489,7 @@
         <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8.82</v>
@@ -10202,7 +10509,7 @@
         <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9.02</v>
@@ -10222,7 +10529,7 @@
         <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -10242,7 +10549,7 @@
         <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -10262,7 +10569,7 @@
         <v>92</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -10279,10 +10586,10 @@
         <v>94</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>7.65</v>

--- a/inasistencias-6A-Tc/Alumnos-6A-Tc.xlsx
+++ b/inasistencias-6A-Tc/Alumnos-6A-Tc.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="364">
   <si>
     <t xml:space="preserve">Teocra de circuitos</t>
   </si>
@@ -36,10 +36,7 @@
     <t xml:space="preserve">total</t>
   </si>
   <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
+    <t xml:space="preserve">Diciembre</t>
   </si>
   <si>
     <t xml:space="preserve">nro</t>
@@ -412,6 +409,9 @@
   </si>
   <si>
     <t xml:space="preserve">no lo intento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cantidad Dic</t>
   </si>
   <si>
     <t xml:space="preserve">Finalizado</t>
@@ -1155,7 +1155,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1170,6 +1170,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF9800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
         <bgColor rgb="FFFF9800"/>
       </patternFill>
@@ -1177,7 +1183,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9800"/>
-        <bgColor rgb="FFFFC107"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1221,7 +1227,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1246,15 +1252,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1266,7 +1272,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1274,11 +1284,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1450,7 +1460,7 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFC107"/>
       <rgbColor rgb="FFFF9800"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -1577,7 +1587,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr defaultColWidth="8.91796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -1593,6 +1603,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="36" min="36" style="1" width="13.76"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="44" min="37" style="1" width="8.92"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="45" min="45" style="2" width="8.92"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="49" min="46" style="0" width="8.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1601,12 +1612,8 @@
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="AY1" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ1" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3"/>
@@ -1618,25 +1625,24 @@
       <c r="Y2" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AY2" s="3" t="s">
+      <c r="AX2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="AY2" s="3"/>
+      <c r="AZ2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>45782</v>
@@ -1651,7 +1657,7 @@
         <v>45807</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>45810</v>
@@ -1660,13 +1666,13 @@
         <v>45814</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>45817</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>45831</v>
@@ -1675,7 +1681,7 @@
         <v>45835</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R3" s="4" t="n">
         <v>45838</v>
@@ -1693,10 +1699,10 @@
         <v>45852</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y3" s="4" t="n">
         <v>45856</v>
@@ -1714,7 +1720,7 @@
         <v>45901</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE3" s="4" t="n">
         <v>45908</v>
@@ -1732,7 +1738,7 @@
         <v>45929</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK3" s="4" t="n">
         <v>45933</v>
@@ -1762,140 +1768,146 @@
         <v>45978</v>
       </c>
       <c r="AT3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AV3" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AW3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+      <c r="AX3" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="AY3" s="6" t="n">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="R4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W4" s="1" t="n">
         <f aca="false">COUNTIF(E4:V4,"P")</f>
         <v>13</v>
       </c>
-      <c r="X4" s="6" t="n">
+      <c r="X4" s="7" t="n">
         <f aca="false">ROUND(W4*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT4" s="3" t="n">
         <f aca="false">COUNTIF(AM4:AR4,"P")</f>
@@ -1909,7 +1921,7 @@
         <f aca="false">COUNTIF(AM4:AR4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AW4" s="6" t="n">
+      <c r="AW4" s="7" t="n">
         <f aca="false">ROUND((AT4+AU4/2+AV4/4)*10/6,0)</f>
         <v>8</v>
       </c>
@@ -1918,121 +1930,121 @@
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W5" s="1" t="n">
         <f aca="false">COUNTIF(E5:V5,"P")</f>
         <v>9</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="X5" s="7" t="n">
         <f aca="false">ROUND(W5*10/$Y$2,0)</f>
         <v>6</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT5" s="3" t="n">
         <f aca="false">COUNTIF(AM5:AR5,"P")</f>
@@ -2046,133 +2058,139 @@
         <f aca="false">COUNTIF(AM5:AR5,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW5" s="6" t="n">
+      <c r="AW5" s="7" t="n">
         <f aca="false">ROUND((AT5+AU5/2+AV5/4)*10/6,0)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY5" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W6" s="1" t="n">
         <f aca="false">COUNTIF(E6:V6,"P")</f>
         <v>13</v>
       </c>
-      <c r="X6" s="6" t="n">
+      <c r="X6" s="7" t="n">
         <f aca="false">ROUND(W6*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT6" s="3" t="n">
         <f aca="false">COUNTIF(AM6:AR6,"P")</f>
@@ -2186,130 +2204,130 @@
         <f aca="false">COUNTIF(AM6:AR6,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="6" t="n">
+      <c r="AW6" s="7" t="n">
         <f aca="false">ROUND((AT6+AU6/2+AV6/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W7" s="1" t="n">
         <f aca="false">COUNTIF(E7:V7,"P")</f>
         <v>14</v>
       </c>
-      <c r="X7" s="6" t="n">
+      <c r="X7" s="7" t="n">
         <f aca="false">ROUND(W7*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT7" s="3" t="n">
         <f aca="false">COUNTIF(AM7:AR7,"P")</f>
@@ -2323,7 +2341,7 @@
         <f aca="false">COUNTIF(AM7:AR7,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW7" s="6" t="n">
+      <c r="AW7" s="7" t="n">
         <f aca="false">ROUND((AT7+AU7/2+AV7/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -2332,121 +2350,121 @@
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W8" s="1" t="n">
         <f aca="false">COUNTIF(E8:V8,"P")</f>
         <v>10</v>
       </c>
-      <c r="X8" s="6" t="n">
+      <c r="X8" s="7" t="n">
         <f aca="false">ROUND(W8*10/$Y$2,0)</f>
         <v>7</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT8" s="3" t="n">
         <f aca="false">COUNTIF(AM8:AR8,"P")</f>
@@ -2460,130 +2478,136 @@
         <f aca="false">COUNTIF(AM8:AR8,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW8" s="6" t="n">
+      <c r="AW8" s="7" t="n">
         <f aca="false">ROUND((AT8+AU8/2+AV8/4)*10/6,0)</f>
         <v>10</v>
+      </c>
+      <c r="AX8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY8" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W9" s="1" t="n">
         <f aca="false">COUNTIF(E9:V9,"P")</f>
         <v>6</v>
       </c>
-      <c r="X9" s="6" t="n">
+      <c r="X9" s="7" t="n">
         <f aca="false">ROUND(W9*10/$Y$2,0)</f>
         <v>4</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT9" s="3" t="n">
         <f aca="false">COUNTIF(AM9:AR9,"P")</f>
@@ -2597,133 +2621,139 @@
         <f aca="false">COUNTIF(AM9:AR9,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW9" s="6" t="n">
+      <c r="AW9" s="7" t="n">
         <f aca="false">ROUND((AT9+AU9/2+AV9/4)*10/6,0)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY9" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W10" s="1" t="n">
         <f aca="false">COUNTIF(E10:V10,"P")</f>
         <v>14</v>
       </c>
-      <c r="X10" s="6" t="n">
+      <c r="X10" s="7" t="n">
         <f aca="false">ROUND(W10*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT10" s="3" t="n">
         <f aca="false">COUNTIF(AM10:AR10,"P")</f>
@@ -2737,130 +2767,130 @@
         <f aca="false">COUNTIF(AM10:AR10,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW10" s="6" t="n">
+      <c r="AW10" s="7" t="n">
         <f aca="false">ROUND((AT10+AU10/2+AV10/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W11" s="1" t="n">
         <f aca="false">COUNTIF(E11:V11,"P")</f>
         <v>14</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <f aca="false">ROUND(W11*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT11" s="3" t="n">
         <f aca="false">COUNTIF(AM11:AR11,"P")</f>
@@ -2874,130 +2904,130 @@
         <f aca="false">COUNTIF(AM11:AR11,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW11" s="6" t="n">
+      <c r="AW11" s="7" t="n">
         <f aca="false">ROUND((AT11+AU11/2+AV11/4)*10/6,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W12" s="1" t="n">
         <f aca="false">COUNTIF(E12:V12,"P")</f>
         <v>14</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="7" t="n">
         <f aca="false">ROUND(W12*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT12" s="3" t="n">
         <f aca="false">COUNTIF(AM12:AR12,"P")</f>
@@ -3011,130 +3041,130 @@
         <f aca="false">COUNTIF(AM12:AR12,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW12" s="6" t="n">
+      <c r="AW12" s="7" t="n">
         <f aca="false">ROUND((AT12+AU12/2+AV12/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W13" s="1" t="n">
         <f aca="false">COUNTIF(E13:V13,"P")</f>
         <v>13</v>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="7" t="n">
         <f aca="false">ROUND(W13*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT13" s="3" t="n">
         <f aca="false">COUNTIF(AM13:AR13,"P")</f>
@@ -3148,133 +3178,133 @@
         <f aca="false">COUNTIF(AM13:AR13,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW13" s="6" t="n">
+      <c r="AW13" s="7" t="n">
         <f aca="false">ROUND((AT13+AU13/2+AV13/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W14" s="1" t="n">
         <f aca="false">COUNTIF(E14:V14,"P")</f>
         <v>13</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <f aca="false">ROUND(W14*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT14" s="3" t="n">
         <f aca="false">COUNTIF(AM14:AR14,"P")</f>
@@ -3288,130 +3318,130 @@
         <f aca="false">COUNTIF(AM14:AR14,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW14" s="6" t="n">
+      <c r="AW14" s="7" t="n">
         <f aca="false">ROUND((AT14+AU14/2+AV14/4)*10/6,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W15" s="1" t="n">
         <f aca="false">COUNTIF(E15:V15,"P")</f>
         <v>12</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="7" t="n">
         <f aca="false">ROUND(W15*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT15" s="3" t="n">
         <f aca="false">COUNTIF(AM15:AR15,"P")</f>
@@ -3425,136 +3455,136 @@
         <f aca="false">COUNTIF(AM15:AR15,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW15" s="6" t="n">
+      <c r="AW15" s="7" t="n">
         <f aca="false">ROUND((AT15+AU15/2+AV15/4)*10/6,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="M16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W16" s="1" t="n">
         <f aca="false">COUNTIF(E16:V16,"P")</f>
         <v>14</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="7" t="n">
         <f aca="false">ROUND(W16*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT16" s="3" t="n">
         <f aca="false">COUNTIF(AM16:AR16,"P")</f>
@@ -3568,130 +3598,130 @@
         <f aca="false">COUNTIF(AM16:AR16,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW16" s="6" t="n">
+      <c r="AW16" s="7" t="n">
         <f aca="false">ROUND((AT16+AU16/2+AV16/4)*10/6,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W17" s="1" t="n">
         <f aca="false">COUNTIF(E17:V17,"P")</f>
         <v>14</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="7" t="n">
         <f aca="false">ROUND(W17*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT17" s="3" t="n">
         <f aca="false">COUNTIF(AM17:AR17,"P")</f>
@@ -3705,130 +3735,130 @@
         <f aca="false">COUNTIF(AM17:AR17,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW17" s="6" t="n">
+      <c r="AW17" s="7" t="n">
         <f aca="false">ROUND((AT17+AU17/2+AV17/4)*10/6,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W18" s="1" t="n">
         <f aca="false">COUNTIF(E18:V18,"P")</f>
         <v>12</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="7" t="n">
         <f aca="false">ROUND(W18*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT18" s="3" t="n">
         <f aca="false">COUNTIF(AM18:AR18,"P")</f>
@@ -3842,7 +3872,7 @@
         <f aca="false">COUNTIF(AM18:AR18,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW18" s="6" t="n">
+      <c r="AW18" s="7" t="n">
         <f aca="false">ROUND((AT18+AU18/2+AV18/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -3851,121 +3881,121 @@
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W19" s="1" t="n">
         <f aca="false">COUNTIF(E19:V19,"P")</f>
         <v>13</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="7" t="n">
         <f aca="false">ROUND(W19*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AM19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT19" s="3" t="n">
         <f aca="false">COUNTIF(AM19:AR19,"P")</f>
@@ -3979,130 +4009,136 @@
         <f aca="false">COUNTIF(AM19:AR19,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW19" s="6" t="n">
+      <c r="AW19" s="7" t="n">
         <f aca="false">ROUND((AT19+AU19/2+AV19/4)*10/6,0)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY19" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W20" s="1" t="n">
         <f aca="false">COUNTIF(E20:V20,"P")</f>
         <v>13</v>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="7" t="n">
         <f aca="false">ROUND(W20*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT20" s="3" t="n">
         <f aca="false">COUNTIF(AM20:AR20,"P")</f>
@@ -4116,130 +4152,130 @@
         <f aca="false">COUNTIF(AM20:AR20,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW20" s="6" t="n">
+      <c r="AW20" s="7" t="n">
         <f aca="false">ROUND((AT20+AU20/2+AV20/4)*10/6,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W21" s="1" t="n">
         <f aca="false">COUNTIF(E21:V21,"P")</f>
         <v>14</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="7" t="n">
         <f aca="false">ROUND(W21*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT21" s="3" t="n">
         <f aca="false">COUNTIF(AM21:AR21,"P")</f>
@@ -4253,130 +4289,130 @@
         <f aca="false">COUNTIF(AM21:AR21,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW21" s="6" t="n">
+      <c r="AW21" s="7" t="n">
         <f aca="false">ROUND((AT21+AU21/2+AV21/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W22" s="1" t="n">
         <f aca="false">COUNTIF(E22:V22,"P")</f>
         <v>13</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="7" t="n">
         <f aca="false">ROUND(W22*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT22" s="3" t="n">
         <f aca="false">COUNTIF(AM22:AR22,"P")</f>
@@ -4390,7 +4426,7 @@
         <f aca="false">COUNTIF(AM22:AR22,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW22" s="6" t="n">
+      <c r="AW22" s="7" t="n">
         <f aca="false">ROUND((AT22+AU22/2+AV22/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -4399,124 +4435,124 @@
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="J23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W23" s="1" t="n">
         <f aca="false">COUNTIF(E23:V23,"P")</f>
         <v>9</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="7" t="n">
         <f aca="false">ROUND(W23*10/$Y$2,0)</f>
         <v>6</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT23" s="3" t="n">
         <f aca="false">COUNTIF(AM23:AR23,"P")</f>
@@ -4530,130 +4566,136 @@
         <f aca="false">COUNTIF(AM23:AR23,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW23" s="6" t="n">
+      <c r="AW23" s="7" t="n">
         <f aca="false">ROUND((AT23+AU23/2+AV23/4)*10/6,0)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY23" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W24" s="1" t="n">
         <f aca="false">COUNTIF(E24:V24,"P")</f>
         <v>14</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="7" t="n">
         <f aca="false">ROUND(W24*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" s="3" t="n">
         <f aca="false">COUNTIF(AM24:AR24,"P")</f>
@@ -4667,133 +4709,133 @@
         <f aca="false">COUNTIF(AM24:AR24,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW24" s="6" t="n">
+      <c r="AW24" s="7" t="n">
         <f aca="false">ROUND((AT24+AU24/2+AV24/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W25" s="1" t="n">
         <f aca="false">COUNTIF(E25:V25,"P")</f>
         <v>14</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="7" t="n">
         <f aca="false">ROUND(W25*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT25" s="3" t="n">
         <f aca="false">COUNTIF(AM25:AR25,"P")</f>
@@ -4807,130 +4849,130 @@
         <f aca="false">COUNTIF(AM25:AR25,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW25" s="6" t="n">
+      <c r="AW25" s="7" t="n">
         <f aca="false">ROUND((AT25+AU25/2+AV25/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W26" s="1" t="n">
         <f aca="false">COUNTIF(E26:V26,"P")</f>
         <v>14</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="7" t="n">
         <f aca="false">ROUND(W26*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS26" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT26" s="3" t="n">
         <f aca="false">COUNTIF(AM26:AR26,"P")</f>
@@ -4944,133 +4986,133 @@
         <f aca="false">COUNTIF(AM26:AR26,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW26" s="6" t="n">
+      <c r="AW26" s="7" t="n">
         <f aca="false">ROUND((AT26+AU26/2+AV26/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="J27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W27" s="1" t="n">
         <f aca="false">COUNTIF(E27:V27,"P")</f>
         <v>14</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="7" t="n">
         <f aca="false">ROUND(W27*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM27" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AN27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS27" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT27" s="3" t="n">
         <f aca="false">COUNTIF(AM27:AR27,"P")</f>
@@ -5084,130 +5126,130 @@
         <f aca="false">COUNTIF(AM27:AR27,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW27" s="6" t="n">
+      <c r="AW27" s="7" t="n">
         <f aca="false">ROUND((AT27+AU27/2+AV27/4)*10/6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W28" s="1" t="n">
         <f aca="false">COUNTIF(E28:V28,"P")</f>
         <v>12</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="7" t="n">
         <f aca="false">ROUND(W28*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS28" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT28" s="3" t="n">
         <f aca="false">COUNTIF(AM28:AR28,"P")</f>
@@ -5221,133 +5263,133 @@
         <f aca="false">COUNTIF(AM28:AR28,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW28" s="6" t="n">
+      <c r="AW28" s="7" t="n">
         <f aca="false">ROUND((AT28+AU28/2+AV28/4)*10/6,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W29" s="1" t="n">
         <f aca="false">COUNTIF(E29:V29,"P")</f>
         <v>12</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" s="7" t="n">
         <f aca="false">ROUND(W29*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT29" s="3" t="n">
         <f aca="false">COUNTIF(AM29:AR29,"P")</f>
@@ -5361,7 +5403,7 @@
         <f aca="false">COUNTIF(AM29:AR29,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW29" s="6" t="n">
+      <c r="AW29" s="7" t="n">
         <f aca="false">ROUND((AT29+AU29/2+AV29/4)*10/6,0)</f>
         <v>8</v>
       </c>
@@ -5498,6 +5540,32 @@
       <c r="AS30" s="2" t="n">
         <f aca="false">COUNTIF(AS4:AS29,"P")</f>
         <v>17</v>
+      </c>
+      <c r="AW30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX30" s="3" t="n">
+        <f aca="false">COUNTIF(AX4:AX29,"P")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AW31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX31" s="3" t="n">
+        <f aca="false">COUNTIF(AX5:AX30,"P")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AW32" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AW33" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5545,7 +5613,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD28"/>
+  <dimension ref="A1:AE29"/>
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -5553,19 +5621,16 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16" min="3" style="1" width="9.75"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="19" style="1" width="9.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="9.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="23" min="22" style="1" width="9.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="27" min="24" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="27" min="19" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="1" width="26.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="3"/>
       <c r="Q1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
@@ -5577,63 +5642,63 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
       <c r="AB1" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S2" s="4" t="n">
         <v>45873</v>
@@ -5642,42 +5707,42 @@
         <v>45877</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="Z2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AB2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>7</v>
@@ -5712,7 +5777,7 @@
       <c r="P3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P3,O3,M3,K3,I3),0)</f>
         <v>8</v>
       </c>
@@ -5720,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>1</v>
@@ -5735,11 +5800,11 @@
         <f aca="false">Y3+Z3/2</f>
         <v>8</v>
       </c>
-      <c r="AB3" s="6" t="n">
+      <c r="AB3" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U3,X3,AA3,Y3),0)</f>
         <v>8</v>
       </c>
-      <c r="AD3" s="6" t="n">
+      <c r="AD3" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q3,AB3),0)</f>
         <v>8</v>
       </c>
@@ -5748,8 +5813,8 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>19</v>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>8</v>
@@ -5796,24 +5861,24 @@
       <c r="P4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P4,O4,M4,K4,I4),0)</f>
         <v>6</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>7</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>1</v>
@@ -5828,20 +5893,20 @@
         <f aca="false">Y4+Z4/2</f>
         <v>8</v>
       </c>
-      <c r="AB4" s="6" t="n">
+      <c r="AB4" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U4,X4,AA4,Y4),0)</f>
         <v>7</v>
       </c>
-      <c r="AD4" s="6" t="n">
+      <c r="AD4" s="7" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>5</v>
@@ -5864,16 +5929,16 @@
         <f aca="false">IF(I5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="10" t="n">
         <v>45850</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="12" t="n">
         <v>45816</v>
       </c>
       <c r="O5" s="1" t="n">
@@ -5882,21 +5947,21 @@
       <c r="P5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P5,O5,M5,K5,I5),0)</f>
         <v>7</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>1</v>
@@ -5911,21 +5976,21 @@
         <f aca="false">Y5+Z5/2</f>
         <v>10</v>
       </c>
-      <c r="AB5" s="6" t="n">
+      <c r="AB5" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U5,X5,AA5,Y5),0)</f>
         <v>7</v>
       </c>
-      <c r="AD5" s="6" t="n">
+      <c r="AD5" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q5,AB5),0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>9</v>
@@ -5960,7 +6025,7 @@
       <c r="P6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P6,O6,M6,K6,I6),0)</f>
         <v>8</v>
       </c>
@@ -5968,7 +6033,7 @@
         <v>9</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>1</v>
@@ -5983,11 +6048,11 @@
         <f aca="false">Y6+Z6/2</f>
         <v>9</v>
       </c>
-      <c r="AB6" s="6" t="n">
+      <c r="AB6" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U6,X6,AA6,Y6),0)</f>
         <v>8</v>
       </c>
-      <c r="AD6" s="6" t="n">
+      <c r="AD6" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q6,AB6),0)</f>
         <v>8</v>
       </c>
@@ -5996,8 +6061,8 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
+      <c r="B7" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>7</v>
@@ -6041,24 +6106,24 @@
       <c r="P7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P7,O7,M7,K7,I7),0)</f>
         <v>6</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>8</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>1</v>
@@ -6073,20 +6138,20 @@
         <f aca="false">Y7+Z7/2</f>
         <v>10</v>
       </c>
-      <c r="AB7" s="6" t="n">
+      <c r="AB7" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U7,X7,AA7,Y7),0)</f>
         <v>9</v>
       </c>
-      <c r="AD7" s="6" t="n">
+      <c r="AD7" s="7" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="8" s="13" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>32</v>
+      <c r="B8" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>9</v>
@@ -6118,33 +6183,30 @@
       <c r="K8" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="2"/>
       <c r="M8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="N8" s="2"/>
       <c r="O8" s="2" t="n">
         <v>3.53</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(P8,O8,M8,K8,I8),0)</f>
         <v>7</v>
       </c>
-      <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W8" s="2" t="n">
         <v>1</v>
@@ -6155,29 +6217,27 @@
       <c r="Y8" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="11" t="n">
+      <c r="AA8" s="14" t="n">
         <f aca="false">Y8+Z8/2</f>
         <v>8</v>
       </c>
-      <c r="AB8" s="12" t="n">
+      <c r="AB8" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U8,X8,AA8,Y8),0)</f>
         <v>7</v>
       </c>
       <c r="AD8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AE8" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="XFD8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AE8" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>7</v>
@@ -6212,7 +6272,7 @@
       <c r="P9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q9" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P9,O9,M9,K9,I9),0)</f>
         <v>9</v>
       </c>
@@ -6220,7 +6280,7 @@
         <v>9</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>7</v>
@@ -6235,21 +6295,21 @@
         <f aca="false">Y9+Z9/2</f>
         <v>10</v>
       </c>
-      <c r="AB9" s="6" t="n">
+      <c r="AB9" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U9,X9,AA9,Y9),0)</f>
         <v>9</v>
       </c>
-      <c r="AD9" s="6" t="n">
+      <c r="AD9" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q9,AB9),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>8</v>
@@ -6284,7 +6344,7 @@
       <c r="P10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P10,O10,M10,K10,I10),0)</f>
         <v>9</v>
       </c>
@@ -6292,7 +6352,7 @@
         <v>9</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>7</v>
@@ -6307,21 +6367,21 @@
         <f aca="false">Y10+Z10/2</f>
         <v>9</v>
       </c>
-      <c r="AB10" s="6" t="n">
+      <c r="AB10" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U10,X10,AA10,Y10),0)</f>
         <v>9</v>
       </c>
-      <c r="AD10" s="6" t="n">
+      <c r="AD10" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q10,AB10),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>9</v>
@@ -6356,7 +6416,7 @@
       <c r="P11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P11,O11,M11,K11,I11),0)</f>
         <v>10</v>
       </c>
@@ -6364,7 +6424,7 @@
         <v>10</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>8</v>
@@ -6382,29 +6442,29 @@
         <f aca="false">Y11+Z11/2</f>
         <v>15</v>
       </c>
-      <c r="AB11" s="6" t="n">
+      <c r="AB11" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U11,X11,AA11,Y11),0)</f>
         <v>10</v>
       </c>
-      <c r="AD11" s="6" t="n">
+      <c r="AD11" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q11,AB11),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="C12" s="15" t="n">
         <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="4" t="n">
@@ -6425,16 +6485,16 @@
         <f aca="false">IF(I12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="10" t="n">
         <v>45877</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="10" t="n">
         <v>45877</v>
       </c>
       <c r="O12" s="1" t="n">
@@ -6443,24 +6503,24 @@
       <c r="P12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P12,O12,M12,K12,I12),0)</f>
         <v>7</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U12" s="1" t="n">
         <v>8</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>7</v>
@@ -6475,21 +6535,21 @@
         <f aca="false">Y12+Z12/2</f>
         <v>10</v>
       </c>
-      <c r="AB12" s="6" t="n">
+      <c r="AB12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U12,X12,AA12,Y12),0)</f>
         <v>8</v>
       </c>
-      <c r="AD12" s="6" t="n">
+      <c r="AD12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q12,AB12),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>10</v>
@@ -6524,7 +6584,7 @@
       <c r="P13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P13,O13,M13,K13,I13),0)</f>
         <v>7</v>
       </c>
@@ -6532,7 +6592,7 @@
         <v>9</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>7</v>
@@ -6547,21 +6607,21 @@
         <f aca="false">Y13+Z13/2</f>
         <v>8</v>
       </c>
-      <c r="AB13" s="6" t="n">
+      <c r="AB13" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U13,X13,AA13,Y13),0)</f>
         <v>8</v>
       </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AD13" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q13,AB13),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>9</v>
@@ -6596,7 +6656,7 @@
       <c r="P14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P14,O14,M14,K14,I14),0)</f>
         <v>9</v>
       </c>
@@ -6604,7 +6664,7 @@
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>8</v>
@@ -6622,21 +6682,21 @@
         <f aca="false">Y14+Z14/2</f>
         <v>24</v>
       </c>
-      <c r="AB14" s="6" t="n">
+      <c r="AB14" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U14,X14,AA14,Y14),0)</f>
         <v>12</v>
       </c>
-      <c r="AD14" s="6" t="n">
+      <c r="AD14" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q14,AB14),0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>8</v>
@@ -6671,7 +6731,7 @@
       <c r="P15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P15,O15,M15,K15,I15),0)</f>
         <v>9</v>
       </c>
@@ -6679,7 +6739,7 @@
         <v>8</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>10</v>
@@ -6697,21 +6757,21 @@
         <f aca="false">Y15+Z15/2</f>
         <v>27</v>
       </c>
-      <c r="AB15" s="6" t="n">
+      <c r="AB15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U15,X15,AA15,Y15),0)</f>
         <v>13</v>
       </c>
-      <c r="AD15" s="6" t="n">
+      <c r="AD15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q15,AB15),0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>8</v>
@@ -6746,7 +6806,7 @@
       <c r="P16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P16,O16,M16,K16,I16),0)</f>
         <v>8</v>
       </c>
@@ -6754,7 +6814,7 @@
         <v>9</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>100</v>
@@ -6772,21 +6832,21 @@
         <f aca="false">Y16+Z16/2</f>
         <v>27</v>
       </c>
-      <c r="AB16" s="6" t="n">
+      <c r="AB16" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U16,X16,AA16,Y16),0)</f>
         <v>13</v>
       </c>
-      <c r="AD16" s="6" t="n">
+      <c r="AD16" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q16,AB16),0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>8</v>
@@ -6809,16 +6869,16 @@
         <f aca="false">IF(I17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="10" t="n">
         <v>45877</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="10" t="n">
         <v>45877</v>
       </c>
       <c r="O17" s="1" t="n">
@@ -6827,18 +6887,18 @@
       <c r="P17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P17,O17,M17,K17,I17),0)</f>
         <v>7</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>8</v>
@@ -6853,11 +6913,11 @@
         <f aca="false">Y17+Z17/2</f>
         <v>10</v>
       </c>
-      <c r="AB17" s="6" t="n">
+      <c r="AB17" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U17,X17,AA17,Y17),0)</f>
         <v>9</v>
       </c>
-      <c r="AD17" s="6" t="n">
+      <c r="AD17" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q17,AB17),0)</f>
         <v>8</v>
       </c>
@@ -6866,8 +6926,8 @@
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>64</v>
+      <c r="B18" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>8</v>
@@ -6902,7 +6962,7 @@
       <c r="P18" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P18,O18,M18,K18,I18),0)</f>
         <v>8</v>
       </c>
@@ -6910,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>1</v>
@@ -6925,23 +6985,23 @@
         <f aca="false">Y18+Z18/2</f>
         <v>9</v>
       </c>
-      <c r="AB18" s="6" t="n">
+      <c r="AB18" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U18,X18,AA18,Y18),0)</f>
         <v>5</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD18" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="AD18" s="7" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>10</v>
@@ -6976,7 +7036,7 @@
       <c r="P19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P19,O19,M19,K19,I19),0)</f>
         <v>8</v>
       </c>
@@ -6993,21 +7053,21 @@
         <f aca="false">Y19+Z19/2</f>
         <v>9</v>
       </c>
-      <c r="AB19" s="6" t="n">
+      <c r="AB19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U19,X19,AA19,Y19),0)</f>
         <v>8</v>
       </c>
-      <c r="AD19" s="6" t="n">
+      <c r="AD19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q19,AB19),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>7</v>
@@ -7042,7 +7102,7 @@
       <c r="P20" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P20,O20,M20,K20,I20),0)</f>
         <v>8</v>
       </c>
@@ -7050,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>8</v>
@@ -7065,21 +7125,21 @@
         <f aca="false">Y20+Z20/2</f>
         <v>10</v>
       </c>
-      <c r="AB20" s="6" t="n">
+      <c r="AB20" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U20,X20,AA20,Y20),0)</f>
         <v>7</v>
       </c>
-      <c r="AD20" s="6" t="n">
+      <c r="AD20" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q20,AB20),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>8</v>
@@ -7114,7 +7174,7 @@
       <c r="P21" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P21,O21,M21,K21,I21),0)</f>
         <v>9</v>
       </c>
@@ -7122,7 +7182,7 @@
         <v>10</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>7</v>
@@ -7137,11 +7197,11 @@
         <f aca="false">Y21+Z21/2</f>
         <v>10</v>
       </c>
-      <c r="AB21" s="6" t="n">
+      <c r="AB21" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U21,X21,AA21,Y21),0)</f>
         <v>9</v>
       </c>
-      <c r="AD21" s="6" t="n">
+      <c r="AD21" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q21,AB21),0)</f>
         <v>9</v>
       </c>
@@ -7150,8 +7210,8 @@
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>77</v>
+      <c r="B22" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>8</v>
@@ -7186,24 +7246,24 @@
       <c r="P22" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P22,O22,M22,K22,I22),0)</f>
         <v>5</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>1</v>
@@ -7218,21 +7278,21 @@
         <f aca="false">Y22+Z22/2</f>
         <v>9</v>
       </c>
-      <c r="AB22" s="6" t="n">
+      <c r="AB22" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U22,X22,AA22,Y22),0)</f>
         <v>7</v>
       </c>
-      <c r="AD22" s="6" t="n">
+      <c r="AD22" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q22,AB22),0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>10</v>
@@ -7267,7 +7327,7 @@
       <c r="P23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P23,O23,M23,K23,I23),0)</f>
         <v>8</v>
       </c>
@@ -7275,7 +7335,7 @@
         <v>10</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>7</v>
@@ -7290,21 +7350,21 @@
         <f aca="false">Y23+Z23/2</f>
         <v>10</v>
       </c>
-      <c r="AB23" s="6" t="n">
+      <c r="AB23" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U23,X23,AA23,Y23),0)</f>
         <v>10</v>
       </c>
-      <c r="AD23" s="6" t="n">
+      <c r="AD23" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q23,AB23),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>9</v>
@@ -7339,7 +7399,7 @@
       <c r="P24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P24,O24,M24,K24,I24),0)</f>
         <v>8</v>
       </c>
@@ -7356,21 +7416,21 @@
         <f aca="false">Y24+Z24/2</f>
         <v>10</v>
       </c>
-      <c r="AB24" s="6" t="n">
+      <c r="AB24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U24,X24,AA24,Y24),0)</f>
         <v>10</v>
       </c>
-      <c r="AD24" s="6" t="n">
+      <c r="AD24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q24,AB24),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>9</v>
@@ -7405,7 +7465,7 @@
       <c r="P25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P25,O25,M25,K25,I25),0)</f>
         <v>11</v>
       </c>
@@ -7422,21 +7482,21 @@
         <f aca="false">Y25+Z25/2</f>
         <v>10</v>
       </c>
-      <c r="AB25" s="6" t="n">
+      <c r="AB25" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U25,X25,AA25,Y25),0)</f>
         <v>10</v>
       </c>
-      <c r="AD25" s="6" t="n">
+      <c r="AD25" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q25,AB25),0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
@@ -7471,7 +7531,7 @@
       <c r="P26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P26,O26,M26,K26,I26),0)</f>
         <v>12</v>
       </c>
@@ -7491,21 +7551,21 @@
         <f aca="false">Y26+Z26/2</f>
         <v>70</v>
       </c>
-      <c r="AB26" s="6" t="n">
+      <c r="AB26" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U26,X26,AA26,Y26),0)</f>
         <v>25</v>
       </c>
-      <c r="AD26" s="6" t="n">
+      <c r="AD26" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q26,AB26),0)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>8</v>
@@ -7540,7 +7600,7 @@
       <c r="P27" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P27,O27,M27,K27,I27),0)</f>
         <v>8</v>
       </c>
@@ -7548,7 +7608,7 @@
         <v>10</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>1</v>
@@ -7563,21 +7623,21 @@
         <f aca="false">Y27+Z27/2</f>
         <v>9</v>
       </c>
-      <c r="AB27" s="6" t="n">
+      <c r="AB27" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U27,X27,AA27,Y27),0)</f>
         <v>8</v>
       </c>
-      <c r="AD27" s="6" t="n">
+      <c r="AD27" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q27,AB27),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>7</v>
@@ -7600,10 +7660,10 @@
         <f aca="false">IF(I28&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="10" t="n">
         <v>45850</v>
       </c>
       <c r="M28" s="1" t="n">
@@ -7615,7 +7675,7 @@
       <c r="P28" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(P28,O28,M28,K28,I28),0)</f>
         <v>8</v>
       </c>
@@ -7623,7 +7683,7 @@
         <v>9</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>8</v>
@@ -7638,13 +7698,22 @@
         <f aca="false">Y28+Z28/2</f>
         <v>8</v>
       </c>
-      <c r="AB28" s="6" t="n">
+      <c r="AB28" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(U28,X28,AA28,Y28),0)</f>
         <v>8</v>
       </c>
-      <c r="AD28" s="6" t="n">
+      <c r="AD28" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(Q28,AB28),0)</f>
         <v>8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD29" s="3" t="n">
+        <f aca="false">COUNTIF(AD3:AD28,"&lt;7")</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7711,7 +7780,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>128</v>
@@ -7723,13 +7792,13 @@
         <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>131</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7737,10 +7806,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>132</v>
@@ -7760,7 +7829,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -7774,10 +7843,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>134</v>
@@ -7802,7 +7871,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>136</v>
@@ -7819,10 +7888,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>138</v>
@@ -7847,7 +7916,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>140</v>
@@ -7864,7 +7933,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -7878,7 +7947,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -7892,10 +7961,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>142</v>
@@ -7920,7 +7989,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>144</v>
@@ -7934,7 +8003,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>146</v>
@@ -7948,7 +8017,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>148</v>
@@ -7962,7 +8031,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>149</v>
@@ -7979,10 +8048,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -7993,7 +8062,7 @@
       <c r="F15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8002,10 +8071,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>144</v>
@@ -8025,7 +8094,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8039,10 +8108,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>154</v>
@@ -8062,10 +8131,10 @@
         <v>12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>156</v>
@@ -8085,10 +8154,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>157</v>
@@ -8113,7 +8182,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>159</v>
@@ -8130,10 +8199,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>161</v>
@@ -8158,7 +8227,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>163</v>
@@ -8172,7 +8241,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>165</v>
@@ -8186,7 +8255,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>167</v>
@@ -8200,7 +8269,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>169</v>
@@ -8214,7 +8283,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>171</v>
@@ -8228,7 +8297,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>172</v>
@@ -8245,10 +8314,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>174</v>
@@ -8273,7 +8342,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>171</v>
@@ -8290,10 +8359,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>177</v>
@@ -8318,7 +8387,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>179</v>
@@ -8332,7 +8401,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>181</v>
@@ -8346,7 +8415,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>183</v>
@@ -8360,7 +8429,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>184</v>
@@ -8374,7 +8443,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>186</v>
@@ -8391,10 +8460,10 @@
         <v>17</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>188</v>
@@ -8414,10 +8483,10 @@
         <v>18</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>149</v>
@@ -8442,7 +8511,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>190</v>
@@ -8459,10 +8528,10 @@
         <v>19</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>192</v>
@@ -8487,7 +8556,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>194</v>
@@ -8504,10 +8573,10 @@
         <v>20</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>196</v>
@@ -8532,7 +8601,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C43" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>151</v>
@@ -8546,7 +8615,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>199</v>
@@ -8560,7 +8629,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>149</v>
@@ -8577,10 +8646,10 @@
         <v>21</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>200</v>
@@ -8600,10 +8669,10 @@
         <v>22</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>202</v>
@@ -8628,7 +8697,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C48" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>203</v>
@@ -8642,7 +8711,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>205</v>
@@ -8656,7 +8725,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>207</v>
@@ -8670,7 +8739,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C51" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>209</v>
@@ -8687,10 +8756,10 @@
         <v>23</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>211</v>
@@ -8715,7 +8784,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C53" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>212</v>
@@ -8732,10 +8801,10 @@
         <v>24</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>214</v>
@@ -8755,10 +8824,10 @@
         <v>25</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>216</v>
@@ -8778,10 +8847,10 @@
         <v>26</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>217</v>
@@ -8823,7 +8892,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>128</v>
@@ -8835,13 +8904,13 @@
         <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>131</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8849,10 +8918,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>219</v>
@@ -8877,7 +8946,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>221</v>
@@ -8894,7 +8963,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -8908,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>223</v>
@@ -8931,10 +9000,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>225</v>
@@ -8954,7 +9023,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8968,7 +9037,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -8982,10 +9051,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>227</v>
@@ -9005,10 +9074,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>229</v>
@@ -9028,10 +9097,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>231</v>
@@ -9056,7 +9125,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>233</v>
@@ -9070,7 +9139,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>235</v>
@@ -9084,7 +9153,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>237</v>
@@ -9101,10 +9170,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>239</v>
@@ -9124,10 +9193,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>241</v>
@@ -9147,10 +9216,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>242</v>
@@ -9170,10 +9239,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>244</v>
@@ -9198,7 +9267,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>246</v>
@@ -9212,7 +9281,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>165</v>
@@ -9226,7 +9295,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>249</v>
@@ -9240,7 +9309,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>251</v>
@@ -9254,7 +9323,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>253</v>
@@ -9271,10 +9340,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>255</v>
@@ -9294,10 +9363,10 @@
         <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>257</v>
@@ -9317,10 +9386,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>259</v>
@@ -9340,10 +9409,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>261</v>
@@ -9363,10 +9432,10 @@
         <v>18</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>263</v>
@@ -9391,7 +9460,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>265</v>
@@ -9405,7 +9474,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>267</v>
@@ -9422,10 +9491,10 @@
         <v>19</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>269</v>
@@ -9445,10 +9514,10 @@
         <v>20</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>271</v>
@@ -9468,10 +9537,10 @@
         <v>21</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>272</v>
@@ -9496,7 +9565,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>274</v>
@@ -9510,7 +9579,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>140</v>
@@ -9524,7 +9593,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>161</v>
@@ -9538,7 +9607,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>278</v>
@@ -9555,10 +9624,10 @@
         <v>22</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>194</v>
@@ -9583,7 +9652,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>281</v>
@@ -9597,7 +9666,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>283</v>
@@ -9611,7 +9680,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>285</v>
@@ -9628,10 +9697,10 @@
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>287</v>
@@ -9651,10 +9720,10 @@
         <v>24</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>242</v>
@@ -9679,7 +9748,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>290</v>
@@ -9693,7 +9762,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>253</v>
@@ -9710,10 +9779,10 @@
         <v>25</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>194</v>
@@ -9738,7 +9807,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>241</v>
@@ -9755,10 +9824,10 @@
         <v>26</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>295</v>
@@ -9798,7 +9867,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>128</v>
@@ -9810,18 +9879,18 @@
         <v>297</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>298</v>
@@ -9846,7 +9915,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>300</v>
@@ -9860,7 +9929,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>302</v>
@@ -9874,7 +9943,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>304</v>
@@ -9913,10 +9982,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="C1" s="4" t="n">
         <v>45772</v>
@@ -9925,7 +9994,7 @@
         <v>45775</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F1" s="4" t="n">
         <v>45835</v>
@@ -9937,7 +10006,7 @@
         <v>45817</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J1" s="4" t="n">
         <v>45887</v>
@@ -9951,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>3</v>
@@ -9976,7 +10045,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="n">
         <f aca="false">SUM(C3:D3)</f>
@@ -9992,7 +10061,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -10011,7 +10080,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>2</v>
@@ -10036,7 +10105,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">SUM(C6:D6)</f>
@@ -10055,7 +10124,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">SUM(C7:D7)</f>
@@ -10071,7 +10140,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="n">
         <f aca="false">SUM(C8:D8)</f>
@@ -10087,7 +10156,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>2</v>
@@ -10109,7 +10178,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>2</v>
@@ -10137,7 +10206,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="n">
         <f aca="false">SUM(C11:D11)</f>
@@ -10159,7 +10228,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -10178,7 +10247,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>3</v>
@@ -10209,7 +10278,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
@@ -10234,7 +10303,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
@@ -10265,7 +10334,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>2</v>
@@ -10287,7 +10356,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="1" t="n">
         <f aca="false">SUM(C17:D17)</f>
@@ -10303,7 +10372,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="n">
         <f aca="false">SUM(C18:D18)</f>
@@ -10322,7 +10391,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1" t="n">
         <f aca="false">SUM(C19:D19)</f>
@@ -10341,7 +10410,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" s="1" t="n">
         <f aca="false">SUM(C20:D20)</f>
@@ -10357,7 +10426,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" s="1" t="n">
         <f aca="false">SUM(C21:D21)</f>
@@ -10376,7 +10445,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
@@ -10401,7 +10470,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>4</v>
@@ -10426,7 +10495,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>6</v>
@@ -10462,7 +10531,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>6</v>
@@ -10495,7 +10564,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>3</v>
@@ -10520,7 +10589,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="1" t="n">
         <f aca="false">SUM(C27:D27)</f>
@@ -10565,10 +10634,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>129</v>
@@ -10577,13 +10646,13 @@
         <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>131</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10591,13 +10660,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>306</v>
@@ -10614,7 +10683,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -10628,7 +10697,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -10642,13 +10711,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>307</v>
@@ -10665,13 +10734,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>308</v>
@@ -10688,13 +10757,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>309</v>
@@ -10711,13 +10780,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>310</v>
@@ -10734,13 +10803,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>311</v>
@@ -10757,13 +10826,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>312</v>
@@ -10780,7 +10849,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -10794,13 +10863,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>313</v>
@@ -10817,13 +10886,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>314</v>
@@ -10840,13 +10909,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>315</v>
@@ -10863,13 +10932,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>316</v>
@@ -10886,7 +10955,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -10900,13 +10969,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>317</v>
@@ -10923,13 +10992,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>318</v>
@@ -10951,10 +11020,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>319</v>
@@ -10968,13 +11037,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>320</v>
@@ -10996,10 +11065,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>321</v>
@@ -11010,10 +11079,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>322</v>
@@ -11024,10 +11093,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>323</v>
@@ -11041,13 +11110,13 @@
         <v>18</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>312</v>
@@ -11064,13 +11133,13 @@
         <v>19</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>324</v>
@@ -11087,13 +11156,13 @@
         <v>20</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>325</v>
@@ -11110,13 +11179,13 @@
         <v>21</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>326</v>
@@ -11133,13 +11202,13 @@
         <v>22</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>327</v>
@@ -11156,13 +11225,13 @@
         <v>23</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>328</v>
@@ -11179,7 +11248,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>1</v>
@@ -11193,7 +11262,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>1</v>
@@ -11238,10 +11307,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>129</v>
@@ -11255,7 +11324,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -11266,7 +11335,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -11277,7 +11346,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -11288,13 +11357,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>329</v>
@@ -11308,7 +11377,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -11319,13 +11388,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>204</v>
@@ -11339,13 +11408,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>330</v>
@@ -11359,13 +11428,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>331</v>
@@ -11379,13 +11448,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>332</v>
@@ -11399,7 +11468,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -11410,7 +11479,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -11421,13 +11490,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>333</v>
@@ -11441,13 +11510,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>213</v>
@@ -11461,13 +11530,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>334</v>
@@ -11481,7 +11550,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -11492,13 +11561,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>213</v>
@@ -11512,13 +11581,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>335</v>
@@ -11532,13 +11601,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>336</v>
@@ -11552,13 +11621,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>147</v>
@@ -11572,7 +11641,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -11583,7 +11652,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -11594,7 +11663,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -11605,13 +11674,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>213</v>
@@ -11625,13 +11694,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>337</v>
@@ -11645,13 +11714,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>338</v>
@@ -11665,10 +11734,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>339</v>
@@ -11715,10 +11784,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>129</v>
@@ -11732,13 +11801,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>341</v>
@@ -11752,13 +11821,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>342</v>
@@ -11772,13 +11841,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>343</v>
@@ -11792,13 +11861,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>344</v>
@@ -11812,7 +11881,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -11823,13 +11892,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>345</v>
@@ -11843,13 +11912,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>346</v>
@@ -11863,13 +11932,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>347</v>
@@ -11883,13 +11952,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>348</v>
@@ -11903,13 +11972,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>349</v>
@@ -11923,13 +11992,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>350</v>
@@ -11943,13 +12012,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>351</v>
@@ -11963,13 +12032,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>352</v>
@@ -11983,13 +12052,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>353</v>
@@ -12003,13 +12072,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>258</v>
@@ -12023,13 +12092,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>354</v>
@@ -12043,7 +12112,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -12054,13 +12123,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>355</v>
@@ -12074,13 +12143,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>356</v>
@@ -12094,13 +12163,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>357</v>
@@ -12114,13 +12183,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>358</v>
@@ -12134,13 +12203,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>359</v>
@@ -12154,13 +12223,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>360</v>
@@ -12174,13 +12243,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>361</v>
@@ -12194,13 +12263,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>362</v>
@@ -12214,10 +12283,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>339</v>

--- a/inasistencias-6A-Tc/Alumnos-6A-Tc.xlsx
+++ b/inasistencias-6A-Tc/Alumnos-6A-Tc.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="365">
   <si>
     <t xml:space="preserve">Teocra de circuitos</t>
   </si>
@@ -66,6 +66,9 @@
     <t xml:space="preserve">tarde</t>
   </si>
   <si>
+    <t xml:space="preserve">Asistencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agasi</t>
   </si>
   <si>
@@ -366,9 +369,6 @@
     <t xml:space="preserve">Evaluacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Asistencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carpeta</t>
   </si>
   <si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t xml:space="preserve">navegacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ausente</t>
   </si>
   <si>
     <t xml:space="preserve">Recuperacion agosto</t>
@@ -1131,7 +1134,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1154,8 +1157,14 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1177,12 +1186,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
-        <bgColor rgb="FFFF9800"/>
+        <bgColor rgb="FFFFBF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9800"/>
+        <bgColor rgb="FFFF8000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFFC107"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4000"/>
         <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
@@ -1227,7 +1254,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1249,10 +1276,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1280,15 +1303,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1457,17 +1504,17 @@
       <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFFC107"/>
       <rgbColor rgb="FFFF9800"/>
       <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -1587,7 +1634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:BB33"/>
   <sheetFormatPr defaultColWidth="8.91796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -1603,7 +1650,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="36" min="36" style="1" width="13.76"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="44" min="37" style="1" width="8.92"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="45" min="45" style="2" width="8.92"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="49" min="46" style="0" width="8.92"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="49" min="46" style="1" width="8.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1782,8 +1829,17 @@
       <c r="AX3" s="4" t="n">
         <v>45992</v>
       </c>
-      <c r="AY3" s="6" t="n">
+      <c r="AY3" s="4" t="n">
         <v>45996</v>
+      </c>
+      <c r="AZ3" s="4" t="n">
+        <v>45999</v>
+      </c>
+      <c r="BA3" s="4" t="n">
+        <v>46003</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1791,123 +1847,123 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W4" s="1" t="n">
         <f aca="false">COUNTIF(E4:V4,"P")</f>
         <v>13</v>
       </c>
-      <c r="X4" s="7" t="n">
+      <c r="X4" s="6" t="n">
         <f aca="false">ROUND(W4*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" s="3" t="n">
         <f aca="false">COUNTIF(AM4:AR4,"P")</f>
@@ -1921,7 +1977,7 @@
         <f aca="false">COUNTIF(AM4:AR4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AW4" s="7" t="n">
+      <c r="AW4" s="6" t="n">
         <f aca="false">ROUND((AT4+AU4/2+AV4/4)*10/6,0)</f>
         <v>8</v>
       </c>
@@ -1930,121 +1986,121 @@
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>18</v>
+      <c r="B5" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W5" s="1" t="n">
         <f aca="false">COUNTIF(E5:V5,"P")</f>
         <v>9</v>
       </c>
-      <c r="X5" s="7" t="n">
+      <c r="X5" s="6" t="n">
         <f aca="false">ROUND(W5*10/$Y$2,0)</f>
         <v>6</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT5" s="3" t="n">
         <f aca="false">COUNTIF(AM5:AR5,"P")</f>
@@ -2058,15 +2114,24 @@
         <f aca="false">COUNTIF(AM5:AR5,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW5" s="7" t="n">
+      <c r="AW5" s="6" t="n">
         <f aca="false">ROUND((AT5+AU5/2+AV5/4)*10/6,0)</f>
         <v>8</v>
       </c>
       <c r="AX5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2074,123 +2139,123 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W6" s="1" t="n">
         <f aca="false">COUNTIF(E6:V6,"P")</f>
         <v>13</v>
       </c>
-      <c r="X6" s="7" t="n">
+      <c r="X6" s="6" t="n">
         <f aca="false">ROUND(W6*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT6" s="3" t="n">
         <f aca="false">COUNTIF(AM6:AR6,"P")</f>
@@ -2204,7 +2269,7 @@
         <f aca="false">COUNTIF(AM6:AR6,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="7" t="n">
+      <c r="AW6" s="6" t="n">
         <f aca="false">ROUND((AT6+AU6/2+AV6/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -2214,120 +2279,120 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W7" s="1" t="n">
         <f aca="false">COUNTIF(E7:V7,"P")</f>
         <v>14</v>
       </c>
-      <c r="X7" s="7" t="n">
+      <c r="X7" s="6" t="n">
         <f aca="false">ROUND(W7*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT7" s="3" t="n">
         <f aca="false">COUNTIF(AM7:AR7,"P")</f>
@@ -2341,7 +2406,7 @@
         <f aca="false">COUNTIF(AM7:AR7,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW7" s="7" t="n">
+      <c r="AW7" s="6" t="n">
         <f aca="false">ROUND((AT7+AU7/2+AV7/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -2350,121 +2415,121 @@
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>28</v>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W8" s="1" t="n">
         <f aca="false">COUNTIF(E8:V8,"P")</f>
         <v>10</v>
       </c>
-      <c r="X8" s="7" t="n">
+      <c r="X8" s="6" t="n">
         <f aca="false">ROUND(W8*10/$Y$2,0)</f>
         <v>7</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT8" s="3" t="n">
         <f aca="false">COUNTIF(AM8:AR8,"P")</f>
@@ -2478,136 +2543,145 @@
         <f aca="false">COUNTIF(AM8:AR8,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW8" s="7" t="n">
+      <c r="AW8" s="6" t="n">
         <f aca="false">ROUND((AT8+AU8/2+AV8/4)*10/6,0)</f>
         <v>10</v>
       </c>
       <c r="AX8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY8" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="AY8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB8" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>31</v>
+      <c r="B9" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W9" s="1" t="n">
         <f aca="false">COUNTIF(E9:V9,"P")</f>
         <v>6</v>
       </c>
-      <c r="X9" s="7" t="n">
+      <c r="X9" s="6" t="n">
         <f aca="false">ROUND(W9*10/$Y$2,0)</f>
         <v>4</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO9" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP9" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT9" s="3" t="n">
         <f aca="false">COUNTIF(AM9:AR9,"P")</f>
@@ -2621,15 +2695,24 @@
         <f aca="false">COUNTIF(AM9:AR9,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW9" s="7" t="n">
+      <c r="AW9" s="6" t="n">
         <f aca="false">ROUND((AT9+AU9/2+AV9/4)*10/6,0)</f>
         <v>8</v>
       </c>
       <c r="AX9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="AY9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB9" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2637,123 +2720,123 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W10" s="1" t="n">
         <f aca="false">COUNTIF(E10:V10,"P")</f>
         <v>14</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="X10" s="6" t="n">
         <f aca="false">ROUND(W10*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT10" s="3" t="n">
         <f aca="false">COUNTIF(AM10:AR10,"P")</f>
@@ -2767,7 +2850,7 @@
         <f aca="false">COUNTIF(AM10:AR10,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW10" s="7" t="n">
+      <c r="AW10" s="6" t="n">
         <f aca="false">ROUND((AT10+AU10/2+AV10/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -2777,120 +2860,120 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W11" s="1" t="n">
         <f aca="false">COUNTIF(E11:V11,"P")</f>
         <v>14</v>
       </c>
-      <c r="X11" s="7" t="n">
+      <c r="X11" s="6" t="n">
         <f aca="false">ROUND(W11*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT11" s="3" t="n">
         <f aca="false">COUNTIF(AM11:AR11,"P")</f>
@@ -2904,7 +2987,7 @@
         <f aca="false">COUNTIF(AM11:AR11,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW11" s="7" t="n">
+      <c r="AW11" s="6" t="n">
         <f aca="false">ROUND((AT11+AU11/2+AV11/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -2914,120 +2997,120 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W12" s="1" t="n">
         <f aca="false">COUNTIF(E12:V12,"P")</f>
         <v>14</v>
       </c>
-      <c r="X12" s="7" t="n">
+      <c r="X12" s="6" t="n">
         <f aca="false">ROUND(W12*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT12" s="3" t="n">
         <f aca="false">COUNTIF(AM12:AR12,"P")</f>
@@ -3041,7 +3124,7 @@
         <f aca="false">COUNTIF(AM12:AR12,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW12" s="7" t="n">
+      <c r="AW12" s="6" t="n">
         <f aca="false">ROUND((AT12+AU12/2+AV12/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -3051,120 +3134,120 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W13" s="1" t="n">
         <f aca="false">COUNTIF(E13:V13,"P")</f>
         <v>13</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="6" t="n">
         <f aca="false">ROUND(W13*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13" s="3" t="n">
         <f aca="false">COUNTIF(AM13:AR13,"P")</f>
@@ -3178,7 +3261,7 @@
         <f aca="false">COUNTIF(AM13:AR13,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW13" s="7" t="n">
+      <c r="AW13" s="6" t="n">
         <f aca="false">ROUND((AT13+AU13/2+AV13/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -3188,123 +3271,123 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W14" s="1" t="n">
         <f aca="false">COUNTIF(E14:V14,"P")</f>
         <v>13</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="X14" s="6" t="n">
         <f aca="false">ROUND(W14*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM14" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO14" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT14" s="3" t="n">
         <f aca="false">COUNTIF(AM14:AR14,"P")</f>
@@ -3318,7 +3401,7 @@
         <f aca="false">COUNTIF(AM14:AR14,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW14" s="7" t="n">
+      <c r="AW14" s="6" t="n">
         <f aca="false">ROUND((AT14+AU14/2+AV14/4)*10/6,0)</f>
         <v>8</v>
       </c>
@@ -3328,120 +3411,120 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W15" s="1" t="n">
         <f aca="false">COUNTIF(E15:V15,"P")</f>
         <v>12</v>
       </c>
-      <c r="X15" s="7" t="n">
+      <c r="X15" s="6" t="n">
         <f aca="false">ROUND(W15*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS15" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT15" s="3" t="n">
         <f aca="false">COUNTIF(AM15:AR15,"P")</f>
@@ -3455,7 +3538,7 @@
         <f aca="false">COUNTIF(AM15:AR15,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW15" s="7" t="n">
+      <c r="AW15" s="6" t="n">
         <f aca="false">ROUND((AT15+AU15/2+AV15/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -3465,126 +3548,126 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W16" s="1" t="n">
         <f aca="false">COUNTIF(E16:V16,"P")</f>
         <v>14</v>
       </c>
-      <c r="X16" s="7" t="n">
+      <c r="X16" s="6" t="n">
         <f aca="false">ROUND(W16*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ16" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS16" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT16" s="3" t="n">
         <f aca="false">COUNTIF(AM16:AR16,"P")</f>
@@ -3598,7 +3681,7 @@
         <f aca="false">COUNTIF(AM16:AR16,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW16" s="7" t="n">
+      <c r="AW16" s="6" t="n">
         <f aca="false">ROUND((AT16+AU16/2+AV16/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -3608,120 +3691,120 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W17" s="1" t="n">
         <f aca="false">COUNTIF(E17:V17,"P")</f>
         <v>14</v>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="6" t="n">
         <f aca="false">ROUND(W17*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM17" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO17" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP17" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ17" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR17" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT17" s="3" t="n">
         <f aca="false">COUNTIF(AM17:AR17,"P")</f>
@@ -3735,7 +3818,7 @@
         <f aca="false">COUNTIF(AM17:AR17,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW17" s="7" t="n">
+      <c r="AW17" s="6" t="n">
         <f aca="false">ROUND((AT17+AU17/2+AV17/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -3745,120 +3828,120 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W18" s="1" t="n">
         <f aca="false">COUNTIF(E18:V18,"P")</f>
         <v>12</v>
       </c>
-      <c r="X18" s="7" t="n">
+      <c r="X18" s="6" t="n">
         <f aca="false">ROUND(W18*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT18" s="3" t="n">
         <f aca="false">COUNTIF(AM18:AR18,"P")</f>
@@ -3872,7 +3955,7 @@
         <f aca="false">COUNTIF(AM18:AR18,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW18" s="7" t="n">
+      <c r="AW18" s="6" t="n">
         <f aca="false">ROUND((AT18+AU18/2+AV18/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -3881,121 +3964,121 @@
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>63</v>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W19" s="1" t="n">
         <f aca="false">COUNTIF(E19:V19,"P")</f>
         <v>13</v>
       </c>
-      <c r="X19" s="7" t="n">
+      <c r="X19" s="6" t="n">
         <f aca="false">ROUND(W19*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL19" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT19" s="3" t="n">
         <f aca="false">COUNTIF(AM19:AR19,"P")</f>
@@ -4009,15 +4092,24 @@
         <f aca="false">COUNTIF(AM19:AR19,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW19" s="7" t="n">
+      <c r="AW19" s="6" t="n">
         <f aca="false">ROUND((AT19+AU19/2+AV19/4)*10/6,0)</f>
         <v>9</v>
       </c>
       <c r="AX19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY19" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="AY19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB19" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4025,120 +4117,120 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W20" s="1" t="n">
         <f aca="false">COUNTIF(E20:V20,"P")</f>
         <v>13</v>
       </c>
-      <c r="X20" s="7" t="n">
+      <c r="X20" s="6" t="n">
         <f aca="false">ROUND(W20*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP20" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT20" s="3" t="n">
         <f aca="false">COUNTIF(AM20:AR20,"P")</f>
@@ -4152,7 +4244,7 @@
         <f aca="false">COUNTIF(AM20:AR20,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW20" s="7" t="n">
+      <c r="AW20" s="6" t="n">
         <f aca="false">ROUND((AT20+AU20/2+AV20/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -4162,120 +4254,120 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W21" s="1" t="n">
         <f aca="false">COUNTIF(E21:V21,"P")</f>
         <v>14</v>
       </c>
-      <c r="X21" s="7" t="n">
+      <c r="X21" s="6" t="n">
         <f aca="false">ROUND(W21*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT21" s="3" t="n">
         <f aca="false">COUNTIF(AM21:AR21,"P")</f>
@@ -4289,7 +4381,7 @@
         <f aca="false">COUNTIF(AM21:AR21,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW21" s="7" t="n">
+      <c r="AW21" s="6" t="n">
         <f aca="false">ROUND((AT21+AU21/2+AV21/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -4299,120 +4391,120 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W22" s="1" t="n">
         <f aca="false">COUNTIF(E22:V22,"P")</f>
         <v>13</v>
       </c>
-      <c r="X22" s="7" t="n">
+      <c r="X22" s="6" t="n">
         <f aca="false">ROUND(W22*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT22" s="3" t="n">
         <f aca="false">COUNTIF(AM22:AR22,"P")</f>
@@ -4426,7 +4518,7 @@
         <f aca="false">COUNTIF(AM22:AR22,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW22" s="7" t="n">
+      <c r="AW22" s="6" t="n">
         <f aca="false">ROUND((AT22+AU22/2+AV22/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -4435,124 +4527,124 @@
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>76</v>
+      <c r="B23" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W23" s="1" t="n">
         <f aca="false">COUNTIF(E23:V23,"P")</f>
         <v>9</v>
       </c>
-      <c r="X23" s="7" t="n">
+      <c r="X23" s="6" t="n">
         <f aca="false">ROUND(W23*10/$Y$2,0)</f>
         <v>6</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM23" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN23" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO23" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ23" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR23" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT23" s="3" t="n">
         <f aca="false">COUNTIF(AM23:AR23,"P")</f>
@@ -4566,15 +4658,24 @@
         <f aca="false">COUNTIF(AM23:AR23,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW23" s="7" t="n">
+      <c r="AW23" s="6" t="n">
         <f aca="false">ROUND((AT23+AU23/2+AV23/4)*10/6,0)</f>
         <v>9</v>
       </c>
       <c r="AX23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY23" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="AY23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB23" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4582,120 +4683,120 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W24" s="1" t="n">
         <f aca="false">COUNTIF(E24:V24,"P")</f>
         <v>14</v>
       </c>
-      <c r="X24" s="7" t="n">
+      <c r="X24" s="6" t="n">
         <f aca="false">ROUND(W24*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT24" s="3" t="n">
         <f aca="false">COUNTIF(AM24:AR24,"P")</f>
@@ -4709,7 +4810,7 @@
         <f aca="false">COUNTIF(AM24:AR24,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW24" s="7" t="n">
+      <c r="AW24" s="6" t="n">
         <f aca="false">ROUND((AT24+AU24/2+AV24/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -4719,123 +4820,123 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W25" s="1" t="n">
         <f aca="false">COUNTIF(E25:V25,"P")</f>
         <v>14</v>
       </c>
-      <c r="X25" s="7" t="n">
+      <c r="X25" s="6" t="n">
         <f aca="false">ROUND(W25*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN25" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO25" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ25" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR25" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT25" s="3" t="n">
         <f aca="false">COUNTIF(AM25:AR25,"P")</f>
@@ -4849,7 +4950,7 @@
         <f aca="false">COUNTIF(AM25:AR25,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW25" s="7" t="n">
+      <c r="AW25" s="6" t="n">
         <f aca="false">ROUND((AT25+AU25/2+AV25/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -4859,120 +4960,120 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W26" s="1" t="n">
         <f aca="false">COUNTIF(E26:V26,"P")</f>
         <v>14</v>
       </c>
-      <c r="X26" s="7" t="n">
+      <c r="X26" s="6" t="n">
         <f aca="false">ROUND(W26*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM26" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN26" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO26" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP26" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR26" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT26" s="3" t="n">
         <f aca="false">COUNTIF(AM26:AR26,"P")</f>
@@ -4986,7 +5087,7 @@
         <f aca="false">COUNTIF(AM26:AR26,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW26" s="7" t="n">
+      <c r="AW26" s="6" t="n">
         <f aca="false">ROUND((AT26+AU26/2+AV26/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -4996,123 +5097,123 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W27" s="1" t="n">
         <f aca="false">COUNTIF(E27:V27,"P")</f>
         <v>14</v>
       </c>
-      <c r="X27" s="7" t="n">
+      <c r="X27" s="6" t="n">
         <f aca="false">ROUND(W27*10/$Y$2,0)</f>
         <v>10</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM27" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AN27" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO27" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP27" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ27" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR27" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT27" s="3" t="n">
         <f aca="false">COUNTIF(AM27:AR27,"P")</f>
@@ -5126,7 +5227,7 @@
         <f aca="false">COUNTIF(AM27:AR27,"A")</f>
         <v>0</v>
       </c>
-      <c r="AW27" s="7" t="n">
+      <c r="AW27" s="6" t="n">
         <f aca="false">ROUND((AT27+AU27/2+AV27/4)*10/6,0)</f>
         <v>10</v>
       </c>
@@ -5136,120 +5237,120 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W28" s="1" t="n">
         <f aca="false">COUNTIF(E28:V28,"P")</f>
         <v>12</v>
       </c>
-      <c r="X28" s="7" t="n">
+      <c r="X28" s="6" t="n">
         <f aca="false">ROUND(W28*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM28" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN28" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO28" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP28" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ28" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR28" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT28" s="3" t="n">
         <f aca="false">COUNTIF(AM28:AR28,"P")</f>
@@ -5263,7 +5364,7 @@
         <f aca="false">COUNTIF(AM28:AR28,"A")</f>
         <v>1</v>
       </c>
-      <c r="AW28" s="7" t="n">
+      <c r="AW28" s="6" t="n">
         <f aca="false">ROUND((AT28+AU28/2+AV28/4)*10/6,0)</f>
         <v>9</v>
       </c>
@@ -5273,123 +5374,123 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W29" s="1" t="n">
         <f aca="false">COUNTIF(E29:V29,"P")</f>
         <v>12</v>
       </c>
-      <c r="X29" s="7" t="n">
+      <c r="X29" s="6" t="n">
         <f aca="false">ROUND(W29*10/$Y$2,0)</f>
         <v>9</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM29" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN29" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP29" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ29" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR29" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT29" s="3" t="n">
         <f aca="false">COUNTIF(AM29:AR29,"P")</f>
@@ -5403,7 +5504,7 @@
         <f aca="false">COUNTIF(AM29:AR29,"A")</f>
         <v>2</v>
       </c>
-      <c r="AW29" s="7" t="n">
+      <c r="AW29" s="6" t="n">
         <f aca="false">ROUND((AT29+AU29/2+AV29/4)*10/6,0)</f>
         <v>8</v>
       </c>
@@ -5613,16 +5714,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AE29"/>
+  <dimension ref="A1:AF29"/>
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.54"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16" min="3" style="1" width="9.75"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.97"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="6" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="27" min="19" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="27" min="19" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="13.14"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="1" width="26.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.58"/>
   </cols>
@@ -5630,7 +5733,7 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="3"/>
       <c r="Q1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
@@ -5642,7 +5745,7 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
       <c r="AB1" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5653,49 +5756,49 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>7</v>
@@ -5722,19 +5825,22 @@
         <v>117</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>118</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="AD2" s="3" t="s">
         <v>119</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5742,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>7</v>
@@ -5800,11 +5906,11 @@
         <f aca="false">Y3+Z3/2</f>
         <v>8</v>
       </c>
-      <c r="AB3" s="7" t="n">
+      <c r="AB3" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U3,X3,AA3,Y3),0)</f>
         <v>8</v>
       </c>
-      <c r="AD3" s="7" t="n">
+      <c r="AD3" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q3,AB3),0)</f>
         <v>8</v>
       </c>
@@ -5813,8 +5919,8 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>18</v>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>8</v>
@@ -5869,10 +5975,10 @@
         <v>121</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>7</v>
@@ -5893,12 +5999,15 @@
         <f aca="false">Y4+Z4/2</f>
         <v>8</v>
       </c>
-      <c r="AB4" s="7" t="n">
+      <c r="AB4" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U4,X4,AA4,Y4),0)</f>
         <v>7</v>
       </c>
-      <c r="AD4" s="7" t="n">
+      <c r="AD4" s="6" t="n">
         <v>6</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5906,7 +6015,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>5</v>
@@ -5929,16 +6038,16 @@
         <f aca="false">IF(I5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="9" t="n">
         <v>45850</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N5" s="11" t="n">
         <v>45816</v>
       </c>
       <c r="O5" s="1" t="n">
@@ -5952,10 +6061,10 @@
         <v>7</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>1</v>
@@ -5976,11 +6085,11 @@
         <f aca="false">Y5+Z5/2</f>
         <v>10</v>
       </c>
-      <c r="AB5" s="7" t="n">
+      <c r="AB5" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U5,X5,AA5,Y5),0)</f>
         <v>7</v>
       </c>
-      <c r="AD5" s="7" t="n">
+      <c r="AD5" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q5,AB5),0)</f>
         <v>7</v>
       </c>
@@ -5990,7 +6099,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>9</v>
@@ -6048,188 +6157,194 @@
         <f aca="false">Y6+Z6/2</f>
         <v>9</v>
       </c>
-      <c r="AB6" s="7" t="n">
+      <c r="AB6" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U6,X6,AA6,Y6),0)</f>
         <v>8</v>
       </c>
-      <c r="AD6" s="7" t="n">
+      <c r="AD6" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q6,AB6),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+    <row r="7" s="12" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="14" t="n">
         <v>45989</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>45989</v>
-      </c>
-      <c r="G7" s="1" t="n">
+      <c r="E7" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="12" t="n">
         <f aca="false">E7+G7/2</f>
-        <v>6</v>
-      </c>
-      <c r="I7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(C7,H7),0)</f>
-        <v>7</v>
-      </c>
-      <c r="J7" s="1" t="str">
+        <v>8</v>
+      </c>
+      <c r="J7" s="12" t="str">
         <f aca="false">IF(I7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K7" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="M7" s="2" t="n">
+      <c r="K7" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="14" t="n">
         <v>45989</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="P7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="17" t="n">
         <f aca="false">ROUND(AVERAGE(P7,O7,M7,K7,I7),0)</f>
         <v>6</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" s="1" t="s">
+      <c r="S7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="U7" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="W7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="X7" s="1" t="n">
+      <c r="X7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="Y7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="3" t="n">
+      <c r="Y7" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="13" t="n">
         <f aca="false">Y7+Z7/2</f>
         <v>10</v>
       </c>
-      <c r="AB7" s="7" t="n">
+      <c r="AB7" s="18" t="n">
         <f aca="false">ROUND(AVERAGE(U7,X7,AA7,Y7),0)</f>
         <v>9</v>
       </c>
-      <c r="AD7" s="7" t="n">
+      <c r="AD7" s="12" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="AF7" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="5" t="n">
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">E8+G8/2</f>
         <v>6</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C8,H8),0)</f>
         <v>8</v>
       </c>
-      <c r="J8" s="2" t="str">
+      <c r="J8" s="1" t="str">
         <f aca="false">IF(I8&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O8" s="2" t="n">
+      <c r="K8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>3.53</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" s="13" t="n">
+      <c r="Q8" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(P8,O8,M8,K8,I8),0)</f>
         <v>7</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U8" s="2" t="n">
+      <c r="S8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="V8" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="W8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="X8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Y8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA8" s="14" t="n">
+      <c r="Y8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="3" t="n">
         <f aca="false">Y8+Z8/2</f>
         <v>8</v>
       </c>
-      <c r="AB8" s="13" t="n">
+      <c r="AB8" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U8,X8,AA8,Y8),0)</f>
         <v>7</v>
       </c>
-      <c r="AD8" s="2" t="n">
+      <c r="AD8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="AE8" s="2" t="s">
-        <v>124</v>
+      <c r="AE8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6237,7 +6352,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>7</v>
@@ -6295,11 +6410,11 @@
         <f aca="false">Y9+Z9/2</f>
         <v>10</v>
       </c>
-      <c r="AB9" s="7" t="n">
+      <c r="AB9" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U9,X9,AA9,Y9),0)</f>
         <v>9</v>
       </c>
-      <c r="AD9" s="7" t="n">
+      <c r="AD9" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q9,AB9),0)</f>
         <v>9</v>
       </c>
@@ -6309,7 +6424,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>8</v>
@@ -6352,7 +6467,7 @@
         <v>9</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>7</v>
@@ -6367,11 +6482,11 @@
         <f aca="false">Y10+Z10/2</f>
         <v>9</v>
       </c>
-      <c r="AB10" s="7" t="n">
+      <c r="AB10" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U10,X10,AA10,Y10),0)</f>
         <v>9</v>
       </c>
-      <c r="AD10" s="7" t="n">
+      <c r="AD10" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q10,AB10),0)</f>
         <v>9</v>
       </c>
@@ -6381,7 +6496,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>9</v>
@@ -6442,11 +6557,11 @@
         <f aca="false">Y11+Z11/2</f>
         <v>15</v>
       </c>
-      <c r="AB11" s="7" t="n">
+      <c r="AB11" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U11,X11,AA11,Y11),0)</f>
         <v>10</v>
       </c>
-      <c r="AD11" s="7" t="n">
+      <c r="AD11" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q11,AB11),0)</f>
         <v>10</v>
       </c>
@@ -6456,15 +6571,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="C12" s="19" t="n">
         <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="19" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="4" t="n">
@@ -6485,16 +6600,16 @@
         <f aca="false">IF(I12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="9" t="n">
         <v>45877</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="9" t="n">
         <v>45877</v>
       </c>
       <c r="O12" s="1" t="n">
@@ -6508,19 +6623,19 @@
         <v>7</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U12" s="1" t="n">
         <v>8</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>7</v>
@@ -6535,11 +6650,11 @@
         <f aca="false">Y12+Z12/2</f>
         <v>10</v>
       </c>
-      <c r="AB12" s="7" t="n">
+      <c r="AB12" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U12,X12,AA12,Y12),0)</f>
         <v>8</v>
       </c>
-      <c r="AD12" s="7" t="n">
+      <c r="AD12" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q12,AB12),0)</f>
         <v>8</v>
       </c>
@@ -6549,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>10</v>
@@ -6592,7 +6707,7 @@
         <v>9</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>7</v>
@@ -6607,11 +6722,11 @@
         <f aca="false">Y13+Z13/2</f>
         <v>8</v>
       </c>
-      <c r="AB13" s="7" t="n">
+      <c r="AB13" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U13,X13,AA13,Y13),0)</f>
         <v>8</v>
       </c>
-      <c r="AD13" s="7" t="n">
+      <c r="AD13" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q13,AB13),0)</f>
         <v>8</v>
       </c>
@@ -6621,7 +6736,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>9</v>
@@ -6682,11 +6797,11 @@
         <f aca="false">Y14+Z14/2</f>
         <v>24</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AB14" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U14,X14,AA14,Y14),0)</f>
         <v>12</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AD14" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q14,AB14),0)</f>
         <v>11</v>
       </c>
@@ -6696,7 +6811,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>8</v>
@@ -6739,7 +6854,7 @@
         <v>8</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>10</v>
@@ -6757,11 +6872,11 @@
         <f aca="false">Y15+Z15/2</f>
         <v>27</v>
       </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AB15" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U15,X15,AA15,Y15),0)</f>
         <v>13</v>
       </c>
-      <c r="AD15" s="7" t="n">
+      <c r="AD15" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q15,AB15),0)</f>
         <v>11</v>
       </c>
@@ -6771,7 +6886,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>8</v>
@@ -6832,11 +6947,11 @@
         <f aca="false">Y16+Z16/2</f>
         <v>27</v>
       </c>
-      <c r="AB16" s="7" t="n">
+      <c r="AB16" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U16,X16,AA16,Y16),0)</f>
         <v>13</v>
       </c>
-      <c r="AD16" s="7" t="n">
+      <c r="AD16" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q16,AB16),0)</f>
         <v>11</v>
       </c>
@@ -6846,7 +6961,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>8</v>
@@ -6869,16 +6984,16 @@
         <f aca="false">IF(I17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="9" t="n">
         <v>45877</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="N17" s="9" t="n">
         <v>45877</v>
       </c>
       <c r="O17" s="1" t="n">
@@ -6892,13 +7007,13 @@
         <v>7</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>8</v>
@@ -6913,11 +7028,11 @@
         <f aca="false">Y17+Z17/2</f>
         <v>10</v>
       </c>
-      <c r="AB17" s="7" t="n">
+      <c r="AB17" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U17,X17,AA17,Y17),0)</f>
         <v>9</v>
       </c>
-      <c r="AD17" s="7" t="n">
+      <c r="AD17" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q17,AB17),0)</f>
         <v>8</v>
       </c>
@@ -6926,8 +7041,8 @@
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>63</v>
+      <c r="B18" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>8</v>
@@ -6985,15 +7100,18 @@
         <f aca="false">Y18+Z18/2</f>
         <v>9</v>
       </c>
-      <c r="AB18" s="7" t="n">
+      <c r="AB18" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U18,X18,AA18,Y18),0)</f>
         <v>5</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD18" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD18" s="6" t="n">
         <v>5</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7001,7 +7119,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>10</v>
@@ -7053,11 +7171,11 @@
         <f aca="false">Y19+Z19/2</f>
         <v>9</v>
       </c>
-      <c r="AB19" s="7" t="n">
+      <c r="AB19" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U19,X19,AA19,Y19),0)</f>
         <v>8</v>
       </c>
-      <c r="AD19" s="7" t="n">
+      <c r="AD19" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q19,AB19),0)</f>
         <v>8</v>
       </c>
@@ -7067,7 +7185,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>7</v>
@@ -7125,11 +7243,11 @@
         <f aca="false">Y20+Z20/2</f>
         <v>10</v>
       </c>
-      <c r="AB20" s="7" t="n">
+      <c r="AB20" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U20,X20,AA20,Y20),0)</f>
         <v>7</v>
       </c>
-      <c r="AD20" s="7" t="n">
+      <c r="AD20" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q20,AB20),0)</f>
         <v>8</v>
       </c>
@@ -7139,7 +7257,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>8</v>
@@ -7182,7 +7300,7 @@
         <v>10</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>7</v>
@@ -7197,94 +7315,100 @@
         <f aca="false">Y21+Z21/2</f>
         <v>10</v>
       </c>
-      <c r="AB21" s="7" t="n">
+      <c r="AB21" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U21,X21,AA21,Y21),0)</f>
         <v>9</v>
       </c>
-      <c r="AD21" s="7" t="n">
+      <c r="AD21" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q21,AB21),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+    <row r="22" s="12" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" s="1" t="n">
+      <c r="B22" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="12" t="n">
         <f aca="false">E22+G22/2</f>
         <v>1</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="I22" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(C22,H22),0)</f>
         <v>5</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="12" t="str">
         <f aca="false">IF(I22&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="K22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" s="1" t="n">
+      <c r="K22" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M22" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O22" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P22" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="17" t="n">
+        <f aca="false">ROUND(AVERAGE(P22,O22,M22,K22,I22),0)</f>
+        <v>6</v>
+      </c>
+      <c r="R22" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="S22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="T22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="U22" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V22" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="W22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <f aca="false">ROUND(AVERAGE(P22,O22,M22,K22,I22),0)</f>
-        <v>5</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="W22" s="1" t="n">
+      <c r="X22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="X22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA22" s="3" t="n">
+      <c r="Y22" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="13" t="n">
         <f aca="false">Y22+Z22/2</f>
         <v>9</v>
       </c>
-      <c r="AB22" s="7" t="n">
+      <c r="AB22" s="18" t="n">
         <f aca="false">ROUND(AVERAGE(U22,X22,AA22,Y22),0)</f>
         <v>7</v>
       </c>
-      <c r="AD22" s="7" t="n">
+      <c r="AD22" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(Q22,AB22),0)</f>
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="AF22" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7292,7 +7416,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>10</v>
@@ -7335,7 +7459,7 @@
         <v>10</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>7</v>
@@ -7350,11 +7474,11 @@
         <f aca="false">Y23+Z23/2</f>
         <v>10</v>
       </c>
-      <c r="AB23" s="7" t="n">
+      <c r="AB23" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U23,X23,AA23,Y23),0)</f>
         <v>10</v>
       </c>
-      <c r="AD23" s="7" t="n">
+      <c r="AD23" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q23,AB23),0)</f>
         <v>9</v>
       </c>
@@ -7364,7 +7488,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>9</v>
@@ -7416,11 +7540,11 @@
         <f aca="false">Y24+Z24/2</f>
         <v>10</v>
       </c>
-      <c r="AB24" s="7" t="n">
+      <c r="AB24" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U24,X24,AA24,Y24),0)</f>
         <v>10</v>
       </c>
-      <c r="AD24" s="7" t="n">
+      <c r="AD24" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q24,AB24),0)</f>
         <v>9</v>
       </c>
@@ -7430,7 +7554,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>9</v>
@@ -7482,11 +7606,11 @@
         <f aca="false">Y25+Z25/2</f>
         <v>10</v>
       </c>
-      <c r="AB25" s="7" t="n">
+      <c r="AB25" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U25,X25,AA25,Y25),0)</f>
         <v>10</v>
       </c>
-      <c r="AD25" s="7" t="n">
+      <c r="AD25" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q25,AB25),0)</f>
         <v>11</v>
       </c>
@@ -7496,7 +7620,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
@@ -7551,11 +7675,11 @@
         <f aca="false">Y26+Z26/2</f>
         <v>70</v>
       </c>
-      <c r="AB26" s="7" t="n">
+      <c r="AB26" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U26,X26,AA26,Y26),0)</f>
         <v>25</v>
       </c>
-      <c r="AD26" s="7" t="n">
+      <c r="AD26" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q26,AB26),0)</f>
         <v>19</v>
       </c>
@@ -7565,7 +7689,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>8</v>
@@ -7623,11 +7747,11 @@
         <f aca="false">Y27+Z27/2</f>
         <v>9</v>
       </c>
-      <c r="AB27" s="7" t="n">
+      <c r="AB27" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U27,X27,AA27,Y27),0)</f>
         <v>8</v>
       </c>
-      <c r="AD27" s="7" t="n">
+      <c r="AD27" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q27,AB27),0)</f>
         <v>8</v>
       </c>
@@ -7637,7 +7761,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>7</v>
@@ -7660,10 +7784,10 @@
         <f aca="false">IF(I28&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" s="9" t="n">
         <v>45850</v>
       </c>
       <c r="M28" s="1" t="n">
@@ -7698,22 +7822,22 @@
         <f aca="false">Y28+Z28/2</f>
         <v>8</v>
       </c>
-      <c r="AB28" s="7" t="n">
+      <c r="AB28" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(U28,X28,AA28,Y28),0)</f>
         <v>8</v>
       </c>
-      <c r="AD28" s="7" t="n">
+      <c r="AD28" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(Q28,AB28),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD29" s="3" t="n">
         <f aca="false">COUNTIF(AD3:AD28,"&lt;7")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7783,19 +7907,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>119</v>
@@ -7806,16 +7930,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -7829,7 +7953,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -7843,16 +7967,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -7871,13 +7995,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -7888,16 +8012,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -7916,13 +8040,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -7933,7 +8057,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -7947,7 +8071,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -7961,16 +8085,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -7989,13 +8113,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -8003,13 +8127,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -8017,13 +8141,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>4</v>
@@ -8031,13 +8155,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>4</v>
@@ -8048,21 +8172,21 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="19" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8071,16 +8195,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -8094,7 +8218,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8108,16 +8232,16 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8131,16 +8255,16 @@
         <v>12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -8154,16 +8278,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -8182,13 +8306,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -8199,16 +8323,16 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -8227,13 +8351,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -8241,13 +8365,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -8255,13 +8379,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -8269,13 +8393,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -8283,13 +8407,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>5</v>
@@ -8297,13 +8421,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>3</v>
@@ -8314,16 +8438,16 @@
         <v>15</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -8342,13 +8466,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>6</v>
@@ -8359,16 +8483,16 @@
         <v>16</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -8387,13 +8511,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>8</v>
@@ -8401,13 +8525,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>6</v>
@@ -8415,13 +8539,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4</v>
@@ -8429,13 +8553,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>2</v>
@@ -8443,13 +8567,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>2</v>
@@ -8460,16 +8584,16 @@
         <v>17</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -8483,16 +8607,16 @@
         <v>18</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -8511,13 +8635,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>5</v>
@@ -8528,16 +8652,16 @@
         <v>19</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -8556,13 +8680,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>5</v>
@@ -8573,16 +8697,16 @@
         <v>20</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -8601,13 +8725,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C43" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>8</v>
@@ -8615,13 +8739,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>8</v>
@@ -8629,13 +8753,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>4</v>
@@ -8646,16 +8770,16 @@
         <v>21</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>10</v>
@@ -8669,16 +8793,16 @@
         <v>22</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>10</v>
@@ -8697,13 +8821,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C48" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>9</v>
@@ -8711,13 +8835,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>9</v>
@@ -8725,13 +8849,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>5</v>
@@ -8739,13 +8863,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C51" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>4</v>
@@ -8756,16 +8880,16 @@
         <v>23</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>10</v>
@@ -8784,13 +8908,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C53" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>7</v>
@@ -8801,16 +8925,16 @@
         <v>24</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>10</v>
@@ -8824,16 +8948,16 @@
         <v>25</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>8</v>
@@ -8847,16 +8971,16 @@
         <v>26</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>7</v>
@@ -8895,19 +9019,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>119</v>
@@ -8918,16 +9042,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -8946,13 +9070,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -8963,7 +9087,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -8977,16 +9101,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -9000,16 +9124,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -9023,7 +9147,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -9037,7 +9161,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -9051,16 +9175,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -9074,16 +9198,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -9097,16 +9221,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>9</v>
@@ -9125,13 +9249,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>9</v>
@@ -9139,13 +9263,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -9153,13 +9277,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>2</v>
@@ -9170,16 +9294,16 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>1</v>
@@ -9193,16 +9317,16 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -9216,16 +9340,16 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -9239,16 +9363,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -9267,13 +9391,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -9281,13 +9405,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -9295,13 +9419,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -9309,13 +9433,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>3</v>
@@ -9323,13 +9447,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>0</v>
@@ -9340,16 +9464,16 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>5</v>
@@ -9363,16 +9487,16 @@
         <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -9386,16 +9510,16 @@
         <v>16</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>8</v>
@@ -9409,16 +9533,16 @@
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -9432,16 +9556,16 @@
         <v>18</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -9460,13 +9584,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -9474,13 +9598,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0</v>
@@ -9491,16 +9615,16 @@
         <v>19</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>8</v>
@@ -9514,16 +9638,16 @@
         <v>20</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>1</v>
@@ -9537,16 +9661,16 @@
         <v>21</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -9565,13 +9689,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -9579,13 +9703,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -9593,13 +9717,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>6</v>
@@ -9607,13 +9731,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>1</v>
@@ -9624,16 +9748,16 @@
         <v>22</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>10</v>
@@ -9652,13 +9776,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>9</v>
@@ -9666,13 +9790,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>8</v>
@@ -9680,13 +9804,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>2</v>
@@ -9697,16 +9821,16 @@
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>9</v>
@@ -9720,16 +9844,16 @@
         <v>24</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -9748,13 +9872,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -9762,13 +9886,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7</v>
@@ -9779,16 +9903,16 @@
         <v>25</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>9</v>
@@ -9807,13 +9931,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>6</v>
@@ -9824,16 +9948,16 @@
         <v>26</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>7</v>
@@ -9870,19 +9994,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>119</v>
@@ -9890,13 +10014,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -9915,13 +10039,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>8</v>
@@ -9929,13 +10053,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>8</v>
@@ -9943,13 +10067,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -9994,7 +10118,7 @@
         <v>45775</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F1" s="4" t="n">
         <v>45835</v>
@@ -10006,7 +10130,7 @@
         <v>45817</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J1" s="4" t="n">
         <v>45887</v>
@@ -10020,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>3</v>
@@ -10045,7 +10169,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="n">
         <f aca="false">SUM(C3:D3)</f>
@@ -10061,7 +10185,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -10080,7 +10204,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>2</v>
@@ -10105,7 +10229,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">SUM(C6:D6)</f>
@@ -10124,7 +10248,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">SUM(C7:D7)</f>
@@ -10140,7 +10264,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="n">
         <f aca="false">SUM(C8:D8)</f>
@@ -10156,7 +10280,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>2</v>
@@ -10178,7 +10302,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>2</v>
@@ -10206,7 +10330,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="n">
         <f aca="false">SUM(C11:D11)</f>
@@ -10228,7 +10352,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -10247,7 +10371,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>3</v>
@@ -10278,7 +10402,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
@@ -10303,7 +10427,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
@@ -10334,7 +10458,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>2</v>
@@ -10356,7 +10480,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="n">
         <f aca="false">SUM(C17:D17)</f>
@@ -10372,7 +10496,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1" t="n">
         <f aca="false">SUM(C18:D18)</f>
@@ -10391,7 +10515,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" s="1" t="n">
         <f aca="false">SUM(C19:D19)</f>
@@ -10410,7 +10534,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20" s="1" t="n">
         <f aca="false">SUM(C20:D20)</f>
@@ -10426,7 +10550,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1" t="n">
         <f aca="false">SUM(C21:D21)</f>
@@ -10445,7 +10569,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
@@ -10470,7 +10594,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>4</v>
@@ -10495,7 +10619,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>6</v>
@@ -10531,7 +10655,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>6</v>
@@ -10564,7 +10688,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>3</v>
@@ -10589,7 +10713,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E27" s="1" t="n">
         <f aca="false">SUM(C27:D27)</f>
@@ -10640,16 +10764,16 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>119</v>
@@ -10660,16 +10784,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -10683,7 +10807,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -10697,7 +10821,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -10711,16 +10835,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -10734,16 +10858,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -10757,16 +10881,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -10780,16 +10904,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -10803,16 +10927,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -10826,16 +10950,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -10849,7 +10973,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -10863,16 +10987,16 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -10886,16 +11010,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -10909,16 +11033,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8</v>
@@ -10932,16 +11056,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -10955,7 +11079,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -10969,16 +11093,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -10992,16 +11116,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -11020,13 +11144,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -11037,16 +11161,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -11065,13 +11189,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -11079,13 +11203,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>5</v>
@@ -11093,13 +11217,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4</v>
@@ -11110,16 +11234,16 @@
         <v>18</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -11133,16 +11257,16 @@
         <v>19</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -11156,16 +11280,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -11179,16 +11303,16 @@
         <v>21</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -11202,16 +11326,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -11225,16 +11349,16 @@
         <v>23</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -11248,7 +11372,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>1</v>
@@ -11262,7 +11386,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>1</v>
@@ -11313,10 +11437,10 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11324,7 +11448,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -11335,7 +11459,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -11346,7 +11470,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -11357,16 +11481,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -11377,7 +11501,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -11388,16 +11512,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -11408,16 +11532,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -11428,16 +11552,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -11448,16 +11572,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -11468,7 +11592,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -11479,7 +11603,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -11490,16 +11614,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -11510,16 +11634,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -11530,16 +11654,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -11550,7 +11674,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -11561,16 +11685,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -11581,16 +11705,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -11601,16 +11725,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -11621,16 +11745,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -11641,7 +11765,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -11652,7 +11776,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -11663,7 +11787,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -11674,16 +11798,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -11694,16 +11818,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -11714,16 +11838,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -11734,16 +11858,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -11790,10 +11914,10 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11801,16 +11925,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -11821,16 +11945,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>5.29</v>
@@ -11841,16 +11965,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8.04</v>
@@ -11861,16 +11985,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>5.49</v>
@@ -11881,7 +12005,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -11892,16 +12016,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3.53</v>
@@ -11912,16 +12036,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7.84</v>
@@ -11932,16 +12056,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7.45</v>
@@ -11952,16 +12076,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -11972,16 +12096,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>5.69</v>
@@ -11992,16 +12116,16 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7.84</v>
@@ -12012,16 +12136,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -12032,16 +12156,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8.43</v>
@@ -12052,16 +12176,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6.86</v>
@@ -12072,16 +12196,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9.61</v>
@@ -12092,16 +12216,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>7.45</v>
@@ -12112,7 +12236,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -12123,16 +12247,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7.84</v>
@@ -12143,16 +12267,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.24</v>
@@ -12163,16 +12287,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>5.1</v>
@@ -12183,16 +12307,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8.82</v>
@@ -12203,16 +12327,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9.02</v>
@@ -12223,16 +12347,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -12243,16 +12367,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -12263,16 +12387,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -12283,16 +12407,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>7.65</v>
